--- a/research/traditional_assets/database/data/kuwait/kuwait_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_shipbuilding_marine.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="kwse_jtc" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,118 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.193</v>
+        <v>0.113</v>
+      </c>
+      <c r="E2">
+        <v>0.168</v>
       </c>
       <c r="G2">
-        <v>0.06782884310618066</v>
+        <v>0.09427443237907206</v>
       </c>
       <c r="H2">
-        <v>0.06782884310618066</v>
+        <v>0.09427443237907206</v>
       </c>
       <c r="I2">
-        <v>-0.006973058637083994</v>
+        <v>0.02541954590325765</v>
       </c>
       <c r="J2">
-        <v>-0.006973058637083994</v>
+        <v>0.02505839653581157</v>
       </c>
       <c r="K2">
-        <v>-51.6</v>
+        <v>37.9</v>
       </c>
       <c r="L2">
-        <v>-0.1635499207606973</v>
+        <v>0.09353405725567619</v>
       </c>
       <c r="M2">
-        <v>0.023</v>
+        <v>7.701000000000001</v>
       </c>
       <c r="N2">
-        <v>0.0003703703703703704</v>
+        <v>0.03613796339746598</v>
       </c>
       <c r="O2">
-        <v>-0.0004457364341085271</v>
+        <v>0.2031926121372032</v>
       </c>
       <c r="P2">
-        <v>0.023</v>
+        <v>7.682</v>
       </c>
       <c r="Q2">
-        <v>0.0003703703703703704</v>
+        <v>0.03604880337869545</v>
       </c>
       <c r="R2">
-        <v>-0.0004457364341085271</v>
+        <v>0.2026912928759895</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.002467212050383067</v>
       </c>
       <c r="U2">
-        <v>16.7</v>
+        <v>16.37</v>
       </c>
       <c r="V2">
-        <v>0.2689210950080515</v>
+        <v>0.07681839511966213</v>
       </c>
       <c r="W2">
-        <v>-0.2918552036199095</v>
+        <v>0.1451621154328098</v>
       </c>
       <c r="X2">
-        <v>0.2925135890030202</v>
+        <v>0.2634492160360715</v>
       </c>
       <c r="Y2">
-        <v>-0.5843687926229297</v>
+        <v>-0.1182871006032617</v>
       </c>
       <c r="Z2">
-        <v>0.5571251986579551</v>
+        <v>0.6748721706833664</v>
       </c>
       <c r="AA2">
-        <v>-0.00388486667843899</v>
+        <v>0.04599027832096018</v>
       </c>
       <c r="AB2">
-        <v>0.06723877674301934</v>
+        <v>0.1154660153155928</v>
       </c>
       <c r="AC2">
-        <v>-0.07112364342145833</v>
+        <v>-0.06947573699463264</v>
       </c>
       <c r="AD2">
-        <v>364.5</v>
+        <v>260.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>364.5</v>
+        <v>260.3</v>
       </c>
       <c r="AG2">
-        <v>347.8</v>
+        <v>243.93</v>
       </c>
       <c r="AH2">
-        <v>0.8544303797468354</v>
+        <v>0.5498521335023236</v>
       </c>
       <c r="AI2">
-        <v>0.7363636363636363</v>
+        <v>0.4653199856989631</v>
       </c>
       <c r="AJ2">
-        <v>0.8484996340570871</v>
+        <v>0.5337286392578168</v>
       </c>
       <c r="AK2">
-        <v>0.7271586870165169</v>
+        <v>0.4492017015634496</v>
       </c>
       <c r="AL2">
-        <v>15.2</v>
+        <v>13.406</v>
       </c>
       <c r="AM2">
-        <v>15.2</v>
+        <v>13.242</v>
       </c>
       <c r="AN2">
-        <v>20.59322033898305</v>
+        <v>6.153664302600474</v>
       </c>
       <c r="AO2">
-        <v>-0.1447368421052632</v>
+        <v>0.7683126958078473</v>
       </c>
       <c r="AP2">
-        <v>19.64971751412429</v>
+        <v>5.766666666666667</v>
       </c>
       <c r="AQ2">
-        <v>-0.1447368421052632</v>
+        <v>0.7778281226400847</v>
       </c>
     </row>
     <row r="3">
@@ -710,127 +715,8970 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Jassim Transport &amp; Stevedoring Company K.S.C. (Closed) (KWSE:JTC)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Shipbuilding &amp; Marine</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0.2691839220462851</v>
+      </c>
+      <c r="H3">
+        <v>0.2691839220462851</v>
+      </c>
+      <c r="I3">
+        <v>0.146163215590743</v>
+      </c>
+      <c r="J3">
+        <v>0.1445817775204169</v>
+      </c>
+      <c r="K3">
+        <v>12.1</v>
+      </c>
+      <c r="L3">
+        <v>0.1473812423873325</v>
+      </c>
+      <c r="M3">
+        <v>7.65</v>
+      </c>
+      <c r="N3">
+        <v>0.04769326683291771</v>
+      </c>
+      <c r="O3">
+        <v>0.6322314049586777</v>
+      </c>
+      <c r="P3">
+        <v>7.65</v>
+      </c>
+      <c r="Q3">
+        <v>0.04769326683291771</v>
+      </c>
+      <c r="R3">
+        <v>0.6322314049586777</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V3">
+        <v>0.06109725685785537</v>
+      </c>
+      <c r="W3">
+        <v>0.08923303834808259</v>
+      </c>
+      <c r="X3">
+        <v>0.1220911900151665</v>
+      </c>
+      <c r="Y3">
+        <v>-0.0328581516670839</v>
+      </c>
+      <c r="Z3">
+        <v>0.6604456600434397</v>
+      </c>
+      <c r="AA3">
+        <v>0.09548840748472552</v>
+      </c>
+      <c r="AB3">
+        <v>0.1136793475353761</v>
+      </c>
+      <c r="AC3">
+        <v>-0.01819094005065063</v>
+      </c>
+      <c r="AD3">
+        <v>20.4</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>20.4</v>
+      </c>
+      <c r="AG3">
+        <v>10.6</v>
+      </c>
+      <c r="AH3">
+        <v>0.1128318584070796</v>
+      </c>
+      <c r="AI3">
+        <v>0.1226698737221888</v>
+      </c>
+      <c r="AJ3">
+        <v>0.06198830409356724</v>
+      </c>
+      <c r="AK3">
+        <v>0.06773162939297123</v>
+      </c>
+      <c r="AL3">
+        <v>0.806</v>
+      </c>
+      <c r="AM3">
+        <v>0.642</v>
+      </c>
+      <c r="AN3">
+        <v>0.7445255474452555</v>
+      </c>
+      <c r="AO3">
+        <v>14.88833746898263</v>
+      </c>
+      <c r="AP3">
+        <v>0.3868613138686131</v>
+      </c>
+      <c r="AQ3">
+        <v>18.69158878504673</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Kuwait and Gulf Link Transport Company K.P.S.C. (KWSE:KGL)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Shipbuilding &amp; Marine</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.113</v>
+      </c>
+      <c r="E4">
+        <v>0.168</v>
+      </c>
+      <c r="G4">
+        <v>0.04982977406375735</v>
+      </c>
+      <c r="H4">
+        <v>0.04982977406375735</v>
+      </c>
+      <c r="I4">
+        <v>-0.005261528938409161</v>
+      </c>
+      <c r="J4">
+        <v>-0.005168950127698984</v>
+      </c>
+      <c r="K4">
+        <v>25.8</v>
+      </c>
+      <c r="L4">
+        <v>0.0798514391829155</v>
+      </c>
+      <c r="M4">
+        <v>0.051</v>
+      </c>
+      <c r="N4">
+        <v>0.000967741935483871</v>
+      </c>
+      <c r="O4">
+        <v>0.001976744186046512</v>
+      </c>
+      <c r="P4">
+        <v>0.032</v>
+      </c>
+      <c r="Q4">
+        <v>0.0006072106261859582</v>
+      </c>
+      <c r="R4">
+        <v>0.00124031007751938</v>
+      </c>
+      <c r="S4">
+        <v>0.019</v>
+      </c>
+      <c r="T4">
+        <v>0.3725490196078431</v>
+      </c>
+      <c r="U4">
+        <v>6.57</v>
+      </c>
+      <c r="V4">
+        <v>0.1246679316888046</v>
+      </c>
+      <c r="W4">
+        <v>0.201091192517537</v>
+      </c>
+      <c r="X4">
+        <v>0.4048072420569765</v>
+      </c>
+      <c r="Y4">
+        <v>-0.2037160495394395</v>
+      </c>
+      <c r="Z4">
+        <v>0.6786389413988658</v>
+      </c>
+      <c r="AA4">
+        <v>-0.003507850842805171</v>
+      </c>
+      <c r="AB4">
+        <v>0.1172526830958095</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1207605339386147</v>
+      </c>
+      <c r="AD4">
+        <v>239.9</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>239.9</v>
+      </c>
+      <c r="AG4">
+        <v>233.33</v>
+      </c>
+      <c r="AH4">
+        <v>0.8198906356801093</v>
+      </c>
+      <c r="AI4">
+        <v>0.6102772831340626</v>
+      </c>
+      <c r="AJ4">
+        <v>0.81575359228053</v>
+      </c>
+      <c r="AK4">
+        <v>0.603653015289887</v>
+      </c>
+      <c r="AL4">
+        <v>12.6</v>
+      </c>
+      <c r="AM4">
+        <v>12.6</v>
+      </c>
+      <c r="AN4">
+        <v>16.1006711409396</v>
+      </c>
+      <c r="AO4">
+        <v>-0.1349206349206349</v>
+      </c>
+      <c r="AP4">
+        <v>15.65973154362416</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.1349206349206349</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Jassim Transport &amp; Stevedoring Company K.S.C. (Closed) (KWSE:JTC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KWSE:JTC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Shipbuilding &amp; Marine</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.11283185840708</v>
+      </c>
+      <c r="F2">
+        <v>0.13</v>
+      </c>
+      <c r="G2">
+        <v>160.4</v>
+      </c>
+      <c r="H2">
+        <v>159.603488356899</v>
+      </c>
+      <c r="I2">
+        <v>171</v>
+      </c>
+      <c r="J2">
+        <v>173.307488356899</v>
+      </c>
+      <c r="K2">
+        <v>20.4</v>
+      </c>
+      <c r="L2">
+        <v>23.504</v>
+      </c>
+      <c r="M2">
+        <v>0.113679347535376</v>
+      </c>
+      <c r="N2">
+        <v>0.112682372596508</v>
+      </c>
+      <c r="O2">
+        <v>0.0475391743119266</v>
+      </c>
+      <c r="P2">
+        <v>0.040205</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.122091190015166</v>
+      </c>
+      <c r="T2">
+        <v>0.123512324823572</v>
+      </c>
+      <c r="U2">
+        <v>1.16795179887204</v>
+      </c>
+      <c r="V2">
+        <v>1.1878796802676</v>
+      </c>
+      <c r="W2">
+        <v>10.79389842509826</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>160.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.07131389334354851</v>
+      </c>
+      <c r="AC2">
+        <v>0.05592844036697248</v>
+      </c>
+      <c r="AD2">
+        <v>0.15</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>27.4</v>
+      </c>
+      <c r="AH2">
+        <v>15.4</v>
+      </c>
+      <c r="AI2">
+        <v>33.5</v>
+      </c>
+      <c r="AJ2">
+        <v>20.4</v>
+      </c>
+      <c r="AK2">
+        <v>20.4</v>
+      </c>
+      <c r="AL2">
+        <v>0.806</v>
+      </c>
+      <c r="AM2">
+        <v>20.4</v>
+      </c>
+      <c r="AN2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1139654488490644</v>
+      </c>
+      <c r="C2">
+        <v>180.1491248254377</v>
+      </c>
+      <c r="D2">
+        <v>170.3491248254377</v>
+      </c>
+      <c r="E2">
+        <v>-20.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H2">
+        <v>160.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>27.4</v>
+      </c>
+      <c r="K2">
+        <v>15.4</v>
+      </c>
+      <c r="L2">
+        <v>12</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>12</v>
+      </c>
+      <c r="O2">
+        <v>1.8</v>
+      </c>
+      <c r="P2">
+        <v>10.2</v>
+      </c>
+      <c r="Q2">
+        <v>25.6</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1139654488490644</v>
+      </c>
+      <c r="T2">
+        <v>1.05400848733586</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1138531506757908</v>
+      </c>
+      <c r="C3">
+        <v>178.5960094687126</v>
+      </c>
       <c r="D3">
-        <v>0.193</v>
+        <v>170.6040094687125</v>
+      </c>
+      <c r="E3">
+        <v>-18.592</v>
+      </c>
+      <c r="F3">
+        <v>1.808</v>
       </c>
       <c r="G3">
-        <v>0.06782884310618066</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H3">
-        <v>0.06782884310618066</v>
+        <v>160.4</v>
       </c>
       <c r="I3">
-        <v>-0.006973058637083994</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-0.006973058637083994</v>
+        <v>27.4</v>
       </c>
       <c r="K3">
-        <v>-51.6</v>
+        <v>15.4</v>
       </c>
       <c r="L3">
-        <v>-0.1635499207606973</v>
+        <v>12</v>
       </c>
       <c r="M3">
-        <v>0.023</v>
+        <v>0.08262560000000001</v>
       </c>
       <c r="N3">
-        <v>0.0003703703703703704</v>
+        <v>11.9173744</v>
       </c>
       <c r="O3">
-        <v>-0.0004457364341085271</v>
+        <v>1.78760616</v>
       </c>
       <c r="P3">
-        <v>0.023</v>
+        <v>10.12976824</v>
       </c>
       <c r="Q3">
-        <v>0.0003703703703703704</v>
+        <v>25.52976824</v>
       </c>
       <c r="R3">
-        <v>-0.0004457364341085271</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.114610808763425</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.06305805515642</v>
       </c>
       <c r="U3">
-        <v>16.7</v>
+        <v>0.0457</v>
       </c>
       <c r="V3">
-        <v>0.2689210950080515</v>
+        <v>0.15</v>
       </c>
       <c r="W3">
-        <v>-0.2918552036199095</v>
-      </c>
-      <c r="X3">
-        <v>0.2925135890030202</v>
+        <v>0.038845</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.5843687926229297</v>
+        <v>145.233438546891</v>
       </c>
       <c r="Z3">
-        <v>0.5571251986579551</v>
-      </c>
-      <c r="AA3">
-        <v>-0.00388486667843899</v>
-      </c>
-      <c r="AB3">
-        <v>0.06723877674301934</v>
-      </c>
-      <c r="AC3">
-        <v>-0.07112364342145833</v>
-      </c>
-      <c r="AD3">
-        <v>364.5</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>364.5</v>
-      </c>
-      <c r="AG3">
-        <v>347.8</v>
-      </c>
-      <c r="AH3">
-        <v>0.8544303797468354</v>
-      </c>
-      <c r="AI3">
-        <v>0.7363636363636363</v>
-      </c>
-      <c r="AJ3">
-        <v>0.8484996340570871</v>
-      </c>
-      <c r="AK3">
-        <v>0.7271586870165169</v>
-      </c>
-      <c r="AL3">
-        <v>15.2</v>
-      </c>
-      <c r="AM3">
-        <v>15.2</v>
-      </c>
-      <c r="AN3">
-        <v>20.59322033898305</v>
-      </c>
-      <c r="AO3">
-        <v>-0.1447368421052632</v>
-      </c>
-      <c r="AP3">
-        <v>19.64971751412429</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.1447368421052632</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1137408525025172</v>
+      </c>
+      <c r="C4">
+        <v>177.0436579965411</v>
+      </c>
+      <c r="D4">
+        <v>170.8596579965411</v>
+      </c>
+      <c r="E4">
+        <v>-16.784</v>
+      </c>
+      <c r="F4">
+        <v>3.616</v>
+      </c>
+      <c r="G4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H4">
+        <v>160.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>27.4</v>
+      </c>
+      <c r="K4">
+        <v>15.4</v>
+      </c>
+      <c r="L4">
+        <v>12</v>
+      </c>
+      <c r="M4">
+        <v>0.1652512</v>
+      </c>
+      <c r="N4">
+        <v>11.8347488</v>
+      </c>
+      <c r="O4">
+        <v>1.77521232</v>
+      </c>
+      <c r="P4">
+        <v>10.05953648</v>
+      </c>
+      <c r="Q4">
+        <v>25.45953648</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1152693392882829</v>
+      </c>
+      <c r="T4">
+        <v>1.072292308034543</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.038845</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>72.61671927344551</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1136285543292436</v>
+      </c>
+      <c r="C5">
+        <v>175.4920738480988</v>
+      </c>
+      <c r="D5">
+        <v>171.1160738480988</v>
+      </c>
+      <c r="E5">
+        <v>-14.976</v>
+      </c>
+      <c r="F5">
+        <v>5.424</v>
+      </c>
+      <c r="G5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H5">
+        <v>160.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>27.4</v>
+      </c>
+      <c r="K5">
+        <v>15.4</v>
+      </c>
+      <c r="L5">
+        <v>12</v>
+      </c>
+      <c r="M5">
+        <v>0.2478768</v>
+      </c>
+      <c r="N5">
+        <v>11.7521232</v>
+      </c>
+      <c r="O5">
+        <v>1.76281848</v>
+      </c>
+      <c r="P5">
+        <v>9.98930472</v>
+      </c>
+      <c r="Q5">
+        <v>25.38930472</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1159414477621068</v>
+      </c>
+      <c r="T5">
+        <v>1.081716957879225</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.038845</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>48.411146182297</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.11351625615597</v>
+      </c>
+      <c r="C6">
+        <v>173.9412604832372</v>
+      </c>
+      <c r="D6">
+        <v>171.3732604832372</v>
+      </c>
+      <c r="E6">
+        <v>-13.168</v>
+      </c>
+      <c r="F6">
+        <v>7.232</v>
+      </c>
+      <c r="G6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H6">
+        <v>160.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>27.4</v>
+      </c>
+      <c r="K6">
+        <v>15.4</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>0.3305024</v>
+      </c>
+      <c r="N6">
+        <v>11.6694976</v>
+      </c>
+      <c r="O6">
+        <v>1.75042464</v>
+      </c>
+      <c r="P6">
+        <v>9.919072959999999</v>
+      </c>
+      <c r="Q6">
+        <v>25.31907296</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1166275584958021</v>
+      </c>
+      <c r="T6">
+        <v>1.091337954595671</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.038845</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>36.30835963672276</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1134039579826964</v>
+      </c>
+      <c r="C7">
+        <v>172.3912213826397</v>
+      </c>
+      <c r="D7">
+        <v>171.6312213826397</v>
+      </c>
+      <c r="E7">
+        <v>-11.36</v>
+      </c>
+      <c r="F7">
+        <v>9.040000000000001</v>
+      </c>
+      <c r="G7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H7">
+        <v>160.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>27.4</v>
+      </c>
+      <c r="K7">
+        <v>15.4</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>0.4131280000000001</v>
+      </c>
+      <c r="N7">
+        <v>11.586872</v>
+      </c>
+      <c r="O7">
+        <v>1.7380308</v>
+      </c>
+      <c r="P7">
+        <v>9.848841199999999</v>
+      </c>
+      <c r="Q7">
+        <v>25.2488412</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1173281136659962</v>
+      </c>
+      <c r="T7">
+        <v>1.101161498611411</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.038845</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>29.0466877093782</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1132916598094228</v>
+      </c>
+      <c r="C8">
+        <v>170.8419600479789</v>
+      </c>
+      <c r="D8">
+        <v>171.8899600479789</v>
+      </c>
+      <c r="E8">
+        <v>-9.551999999999998</v>
+      </c>
+      <c r="F8">
+        <v>10.848</v>
+      </c>
+      <c r="G8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H8">
+        <v>160.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>27.4</v>
+      </c>
+      <c r="K8">
+        <v>15.4</v>
+      </c>
+      <c r="L8">
+        <v>12</v>
+      </c>
+      <c r="M8">
+        <v>0.4957536000000001</v>
+      </c>
+      <c r="N8">
+        <v>11.5042464</v>
+      </c>
+      <c r="O8">
+        <v>1.72563696</v>
+      </c>
+      <c r="P8">
+        <v>9.77860944</v>
+      </c>
+      <c r="Q8">
+        <v>25.17860944</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1180435742653434</v>
+      </c>
+      <c r="T8">
+        <v>1.111194054201954</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.038845</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>24.2055730911485</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1131793616361492</v>
+      </c>
+      <c r="C9">
+        <v>169.2934800020743</v>
+      </c>
+      <c r="D9">
+        <v>172.1494800020743</v>
+      </c>
+      <c r="E9">
+        <v>-7.743999999999996</v>
+      </c>
+      <c r="F9">
+        <v>12.656</v>
+      </c>
+      <c r="G9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H9">
+        <v>160.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>27.4</v>
+      </c>
+      <c r="K9">
+        <v>15.4</v>
+      </c>
+      <c r="L9">
+        <v>12</v>
+      </c>
+      <c r="M9">
+        <v>0.5783792000000002</v>
+      </c>
+      <c r="N9">
+        <v>11.4216208</v>
+      </c>
+      <c r="O9">
+        <v>1.71324312</v>
+      </c>
+      <c r="P9">
+        <v>9.70837768</v>
+      </c>
+      <c r="Q9">
+        <v>25.10837768</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.118774421114139</v>
+      </c>
+      <c r="T9">
+        <v>1.121442363676165</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.038845</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>20.74763407812728</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1130670634628756</v>
+      </c>
+      <c r="C10">
+        <v>167.7457847890529</v>
+      </c>
+      <c r="D10">
+        <v>172.4097847890529</v>
+      </c>
+      <c r="E10">
+        <v>-5.935999999999998</v>
+      </c>
+      <c r="F10">
+        <v>14.464</v>
+      </c>
+      <c r="G10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H10">
+        <v>160.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>27.4</v>
+      </c>
+      <c r="K10">
+        <v>15.4</v>
+      </c>
+      <c r="L10">
+        <v>12</v>
+      </c>
+      <c r="M10">
+        <v>0.6610048000000001</v>
+      </c>
+      <c r="N10">
+        <v>11.3389952</v>
+      </c>
+      <c r="O10">
+        <v>1.70084928</v>
+      </c>
+      <c r="P10">
+        <v>9.638145919999999</v>
+      </c>
+      <c r="Q10">
+        <v>25.03814592</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1195211559379083</v>
+      </c>
+      <c r="T10">
+        <v>1.131913462486771</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.038845</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>18.15417981836138</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.112954765289602</v>
+      </c>
+      <c r="C11">
+        <v>166.1988779745103</v>
+      </c>
+      <c r="D11">
+        <v>172.6708779745103</v>
+      </c>
+      <c r="E11">
+        <v>-4.127999999999997</v>
+      </c>
+      <c r="F11">
+        <v>16.272</v>
+      </c>
+      <c r="G11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H11">
+        <v>160.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>27.4</v>
+      </c>
+      <c r="K11">
+        <v>15.4</v>
+      </c>
+      <c r="L11">
+        <v>12</v>
+      </c>
+      <c r="M11">
+        <v>0.7436304000000001</v>
+      </c>
+      <c r="N11">
+        <v>11.2563696</v>
+      </c>
+      <c r="O11">
+        <v>1.68845544</v>
+      </c>
+      <c r="P11">
+        <v>9.567914159999999</v>
+      </c>
+      <c r="Q11">
+        <v>24.96791416</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1202843025160462</v>
+      </c>
+      <c r="T11">
+        <v>1.142614695337171</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.038845</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>16.13704872743233</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1128424671163284</v>
+      </c>
+      <c r="C12">
+        <v>164.6527631456732</v>
+      </c>
+      <c r="D12">
+        <v>172.9327631456732</v>
+      </c>
+      <c r="E12">
+        <v>-2.319999999999997</v>
+      </c>
+      <c r="F12">
+        <v>18.08</v>
+      </c>
+      <c r="G12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H12">
+        <v>160.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>27.4</v>
+      </c>
+      <c r="K12">
+        <v>15.4</v>
+      </c>
+      <c r="L12">
+        <v>12</v>
+      </c>
+      <c r="M12">
+        <v>0.8262560000000002</v>
+      </c>
+      <c r="N12">
+        <v>11.173744</v>
+      </c>
+      <c r="O12">
+        <v>1.6760616</v>
+      </c>
+      <c r="P12">
+        <v>9.497682399999999</v>
+      </c>
+      <c r="Q12">
+        <v>24.8976824</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1210644079070316</v>
+      </c>
+      <c r="T12">
+        <v>1.153553733362024</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.038845</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>14.5233438546891</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1127301689430548</v>
+      </c>
+      <c r="C13">
+        <v>163.1074439115642</v>
+      </c>
+      <c r="D13">
+        <v>173.1954439115642</v>
+      </c>
+      <c r="E13">
+        <v>-0.5119999999999969</v>
+      </c>
+      <c r="F13">
+        <v>19.888</v>
+      </c>
+      <c r="G13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H13">
+        <v>160.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>27.4</v>
+      </c>
+      <c r="K13">
+        <v>15.4</v>
+      </c>
+      <c r="L13">
+        <v>12</v>
+      </c>
+      <c r="M13">
+        <v>0.9088816000000002</v>
+      </c>
+      <c r="N13">
+        <v>11.0911184</v>
+      </c>
+      <c r="O13">
+        <v>1.66366776</v>
+      </c>
+      <c r="P13">
+        <v>9.42745064</v>
+      </c>
+      <c r="Q13">
+        <v>24.82745064</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1218620437562414</v>
+      </c>
+      <c r="T13">
+        <v>1.164738592466088</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.038845</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>13.20303986789918</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1127810707697812</v>
+      </c>
+      <c r="C14">
+        <v>161.1802787739951</v>
+      </c>
+      <c r="D14">
+        <v>173.0762787739951</v>
+      </c>
+      <c r="E14">
+        <v>1.296000000000003</v>
+      </c>
+      <c r="F14">
+        <v>21.696</v>
+      </c>
+      <c r="G14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H14">
+        <v>160.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>27.4</v>
+      </c>
+      <c r="K14">
+        <v>15.4</v>
+      </c>
+      <c r="L14">
+        <v>12</v>
+      </c>
+      <c r="M14">
+        <v>1.0262208</v>
+      </c>
+      <c r="N14">
+        <v>10.9737792</v>
+      </c>
+      <c r="O14">
+        <v>1.64606688</v>
+      </c>
+      <c r="P14">
+        <v>9.32771232</v>
+      </c>
+      <c r="Q14">
+        <v>24.72771232</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1226778076929332</v>
+      </c>
+      <c r="T14">
+        <v>1.176177652913425</v>
+      </c>
+      <c r="U14">
+        <v>0.0473</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.040205</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>11.69338996052311</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1126823725965077</v>
+      </c>
+      <c r="C15">
+        <v>159.603488356899</v>
+      </c>
+      <c r="D15">
+        <v>173.3074883568989</v>
+      </c>
+      <c r="E15">
+        <v>3.104000000000003</v>
+      </c>
+      <c r="F15">
+        <v>23.504</v>
+      </c>
+      <c r="G15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H15">
+        <v>160.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>27.4</v>
+      </c>
+      <c r="K15">
+        <v>15.4</v>
+      </c>
+      <c r="L15">
+        <v>12</v>
+      </c>
+      <c r="M15">
+        <v>1.1117392</v>
+      </c>
+      <c r="N15">
+        <v>10.8882608</v>
+      </c>
+      <c r="O15">
+        <v>1.63323912</v>
+      </c>
+      <c r="P15">
+        <v>9.255021679999999</v>
+      </c>
+      <c r="Q15">
+        <v>24.65502168</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.123512324823572</v>
+      </c>
+      <c r="T15">
+        <v>1.187879680267598</v>
+      </c>
+      <c r="U15">
+        <v>0.0473</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.040205</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>10.79389842509826</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.113035874423234</v>
+      </c>
+      <c r="C16">
+        <v>156.9702200591183</v>
+      </c>
+      <c r="D16">
+        <v>172.4822200591183</v>
+      </c>
+      <c r="E16">
+        <v>4.912000000000006</v>
+      </c>
+      <c r="F16">
+        <v>25.312</v>
+      </c>
+      <c r="G16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H16">
+        <v>160.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>27.4</v>
+      </c>
+      <c r="K16">
+        <v>15.4</v>
+      </c>
+      <c r="L16">
+        <v>12</v>
+      </c>
+      <c r="M16">
+        <v>1.2934432</v>
+      </c>
+      <c r="N16">
+        <v>10.7065568</v>
+      </c>
+      <c r="O16">
+        <v>1.60598352</v>
+      </c>
+      <c r="P16">
+        <v>9.100573279999999</v>
+      </c>
+      <c r="Q16">
+        <v>24.50057328</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1243662493293419</v>
+      </c>
+      <c r="T16">
+        <v>1.199853847792798</v>
+      </c>
+      <c r="U16">
+        <v>0.0511</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.043435</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>9.277562400884706</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1129694762499604</v>
+      </c>
+      <c r="C17">
+        <v>155.3166299985319</v>
+      </c>
+      <c r="D17">
+        <v>172.6366299985319</v>
+      </c>
+      <c r="E17">
+        <v>6.720000000000002</v>
+      </c>
+      <c r="F17">
+        <v>27.12</v>
+      </c>
+      <c r="G17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H17">
+        <v>160.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>27.4</v>
+      </c>
+      <c r="K17">
+        <v>15.4</v>
+      </c>
+      <c r="L17">
+        <v>12</v>
+      </c>
+      <c r="M17">
+        <v>1.385832</v>
+      </c>
+      <c r="N17">
+        <v>10.614168</v>
+      </c>
+      <c r="O17">
+        <v>1.5921252</v>
+      </c>
+      <c r="P17">
+        <v>9.022042799999999</v>
+      </c>
+      <c r="Q17">
+        <v>24.4220428</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1252402661764241</v>
+      </c>
+      <c r="T17">
+        <v>1.212109760436239</v>
+      </c>
+      <c r="U17">
+        <v>0.0511</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.043435</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.659058240825727</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1129030780766868</v>
+      </c>
+      <c r="C18">
+        <v>153.6633166481222</v>
+      </c>
+      <c r="D18">
+        <v>172.7913166481222</v>
+      </c>
+      <c r="E18">
+        <v>8.528000000000002</v>
+      </c>
+      <c r="F18">
+        <v>28.928</v>
+      </c>
+      <c r="G18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H18">
+        <v>160.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>27.4</v>
+      </c>
+      <c r="K18">
+        <v>15.4</v>
+      </c>
+      <c r="L18">
+        <v>12</v>
+      </c>
+      <c r="M18">
+        <v>1.4782208</v>
+      </c>
+      <c r="N18">
+        <v>10.5217792</v>
+      </c>
+      <c r="O18">
+        <v>1.57826688</v>
+      </c>
+      <c r="P18">
+        <v>8.94351232</v>
+      </c>
+      <c r="Q18">
+        <v>24.34351232</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1261350929484367</v>
+      </c>
+      <c r="T18">
+        <v>1.22465748052357</v>
+      </c>
+      <c r="U18">
+        <v>0.0511</v>
+      </c>
+      <c r="V18">
+        <v>0.15</v>
+      </c>
+      <c r="W18">
+        <v>0.043435</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>8.117867100774118</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1131112299034133</v>
+      </c>
+      <c r="C19">
+        <v>151.3713140518859</v>
+      </c>
+      <c r="D19">
+        <v>172.3073140518858</v>
+      </c>
+      <c r="E19">
+        <v>10.33600000000001</v>
+      </c>
+      <c r="F19">
+        <v>30.736</v>
+      </c>
+      <c r="G19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H19">
+        <v>160.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>27.4</v>
+      </c>
+      <c r="K19">
+        <v>15.4</v>
+      </c>
+      <c r="L19">
+        <v>12</v>
+      </c>
+      <c r="M19">
+        <v>1.629008</v>
+      </c>
+      <c r="N19">
+        <v>10.370992</v>
+      </c>
+      <c r="O19">
+        <v>1.5556488</v>
+      </c>
+      <c r="P19">
+        <v>8.815343199999999</v>
+      </c>
+      <c r="Q19">
+        <v>24.2153432</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1270514818113413</v>
+      </c>
+      <c r="T19">
+        <v>1.237507555311802</v>
+      </c>
+      <c r="U19">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0.15</v>
+      </c>
+      <c r="W19">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>7.366446328072051</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1130609817301397</v>
+      </c>
+      <c r="C20">
+        <v>149.6799045893534</v>
+      </c>
+      <c r="D20">
+        <v>172.4239045893534</v>
+      </c>
+      <c r="E20">
+        <v>12.14400000000001</v>
+      </c>
+      <c r="F20">
+        <v>32.544</v>
+      </c>
+      <c r="G20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H20">
+        <v>160.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>27.4</v>
+      </c>
+      <c r="K20">
+        <v>15.4</v>
+      </c>
+      <c r="L20">
+        <v>12</v>
+      </c>
+      <c r="M20">
+        <v>1.724832</v>
+      </c>
+      <c r="N20">
+        <v>10.275168</v>
+      </c>
+      <c r="O20">
+        <v>1.5412752</v>
+      </c>
+      <c r="P20">
+        <v>8.7338928</v>
+      </c>
+      <c r="Q20">
+        <v>24.1338928</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1279902216221215</v>
+      </c>
+      <c r="T20">
+        <v>1.250671046558282</v>
+      </c>
+      <c r="U20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.15</v>
+      </c>
+      <c r="W20">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.957199309845826</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1130107335568661</v>
+      </c>
+      <c r="C21">
+        <v>147.9886530139958</v>
+      </c>
+      <c r="D21">
+        <v>172.5406530139958</v>
+      </c>
+      <c r="E21">
+        <v>13.95200000000001</v>
+      </c>
+      <c r="F21">
+        <v>34.352</v>
+      </c>
+      <c r="G21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H21">
+        <v>160.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>27.4</v>
+      </c>
+      <c r="K21">
+        <v>15.4</v>
+      </c>
+      <c r="L21">
+        <v>12</v>
+      </c>
+      <c r="M21">
+        <v>1.820656</v>
+      </c>
+      <c r="N21">
+        <v>10.179344</v>
+      </c>
+      <c r="O21">
+        <v>1.5269016</v>
+      </c>
+      <c r="P21">
+        <v>8.6524424</v>
+      </c>
+      <c r="Q21">
+        <v>24.0524424</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1289521401936618</v>
+      </c>
+      <c r="T21">
+        <v>1.264159562279985</v>
+      </c>
+      <c r="U21">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.15</v>
+      </c>
+      <c r="W21">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>6.591030925117099</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1129604853835925</v>
+      </c>
+      <c r="C22">
+        <v>146.2975596467469</v>
+      </c>
+      <c r="D22">
+        <v>172.6575596467469</v>
+      </c>
+      <c r="E22">
+        <v>15.76000000000001</v>
+      </c>
+      <c r="F22">
+        <v>36.16</v>
+      </c>
+      <c r="G22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H22">
+        <v>160.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>27.4</v>
+      </c>
+      <c r="K22">
+        <v>15.4</v>
+      </c>
+      <c r="L22">
+        <v>12</v>
+      </c>
+      <c r="M22">
+        <v>1.91648</v>
+      </c>
+      <c r="N22">
+        <v>10.08352</v>
+      </c>
+      <c r="O22">
+        <v>1.512528</v>
+      </c>
+      <c r="P22">
+        <v>8.570992</v>
+      </c>
+      <c r="Q22">
+        <v>23.970992</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1299381067294906</v>
+      </c>
+      <c r="T22">
+        <v>1.27798529089473</v>
+      </c>
+      <c r="U22">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.15</v>
+      </c>
+      <c r="W22">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>6.261479378861244</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1132672372103189</v>
+      </c>
+      <c r="C23">
+        <v>143.7783338271267</v>
+      </c>
+      <c r="D23">
+        <v>171.9463338271267</v>
+      </c>
+      <c r="E23">
+        <v>17.568</v>
+      </c>
+      <c r="F23">
+        <v>37.968</v>
+      </c>
+      <c r="G23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H23">
+        <v>160.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>27.4</v>
+      </c>
+      <c r="K23">
+        <v>15.4</v>
+      </c>
+      <c r="L23">
+        <v>12</v>
+      </c>
+      <c r="M23">
+        <v>2.08824</v>
+      </c>
+      <c r="N23">
+        <v>9.911759999999999</v>
+      </c>
+      <c r="O23">
+        <v>1.486764</v>
+      </c>
+      <c r="P23">
+        <v>8.424995999999998</v>
+      </c>
+      <c r="Q23">
+        <v>23.824996</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1309490344434416</v>
+      </c>
+      <c r="T23">
+        <v>1.292161037955418</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0.15</v>
+      </c>
+      <c r="W23">
+        <v>0.04675</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.746465923457073</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1132339890370453</v>
+      </c>
+      <c r="C24">
+        <v>142.0471388133273</v>
+      </c>
+      <c r="D24">
+        <v>172.0231388133273</v>
+      </c>
+      <c r="E24">
+        <v>19.376</v>
+      </c>
+      <c r="F24">
+        <v>39.776</v>
+      </c>
+      <c r="G24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H24">
+        <v>160.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>27.4</v>
+      </c>
+      <c r="K24">
+        <v>15.4</v>
+      </c>
+      <c r="L24">
+        <v>12</v>
+      </c>
+      <c r="M24">
+        <v>2.18768</v>
+      </c>
+      <c r="N24">
+        <v>9.81232</v>
+      </c>
+      <c r="O24">
+        <v>1.471848</v>
+      </c>
+      <c r="P24">
+        <v>8.340472</v>
+      </c>
+      <c r="Q24">
+        <v>23.740472</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1319858833808273</v>
+      </c>
+      <c r="T24">
+        <v>1.30670026570997</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0.15</v>
+      </c>
+      <c r="W24">
+        <v>0.04675</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.485262926936297</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1132007408637717</v>
+      </c>
+      <c r="C25">
+        <v>140.3160124446908</v>
+      </c>
+      <c r="D25">
+        <v>172.1000124446908</v>
+      </c>
+      <c r="E25">
+        <v>21.184</v>
+      </c>
+      <c r="F25">
+        <v>41.584</v>
+      </c>
+      <c r="G25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H25">
+        <v>160.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>27.4</v>
+      </c>
+      <c r="K25">
+        <v>15.4</v>
+      </c>
+      <c r="L25">
+        <v>12</v>
+      </c>
+      <c r="M25">
+        <v>2.28712</v>
+      </c>
+      <c r="N25">
+        <v>9.71288</v>
+      </c>
+      <c r="O25">
+        <v>1.456932</v>
+      </c>
+      <c r="P25">
+        <v>8.255948</v>
+      </c>
+      <c r="Q25">
+        <v>23.655948</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1330496634594437</v>
+      </c>
+      <c r="T25">
+        <v>1.32161713574386</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.15</v>
+      </c>
+      <c r="W25">
+        <v>0.04675</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.246773234460806</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1131674926904981</v>
+      </c>
+      <c r="C26">
+        <v>138.5849548132868</v>
+      </c>
+      <c r="D26">
+        <v>172.1769548132868</v>
+      </c>
+      <c r="E26">
+        <v>22.992</v>
+      </c>
+      <c r="F26">
+        <v>43.392</v>
+      </c>
+      <c r="G26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H26">
+        <v>160.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>27.4</v>
+      </c>
+      <c r="K26">
+        <v>15.4</v>
+      </c>
+      <c r="L26">
+        <v>12</v>
+      </c>
+      <c r="M26">
+        <v>2.38656</v>
+      </c>
+      <c r="N26">
+        <v>9.613440000000001</v>
+      </c>
+      <c r="O26">
+        <v>1.442016</v>
+      </c>
+      <c r="P26">
+        <v>8.171424</v>
+      </c>
+      <c r="Q26">
+        <v>23.571424</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1341414377506554</v>
+      </c>
+      <c r="T26">
+        <v>1.336926554989169</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.15</v>
+      </c>
+      <c r="W26">
+        <v>0.04675</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>5.02815768302494</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1131342445172245</v>
+      </c>
+      <c r="C27">
+        <v>136.8539660113494</v>
+      </c>
+      <c r="D27">
+        <v>172.2539660113494</v>
+      </c>
+      <c r="E27">
+        <v>24.8</v>
+      </c>
+      <c r="F27">
+        <v>45.2</v>
+      </c>
+      <c r="G27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H27">
+        <v>160.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>27.4</v>
+      </c>
+      <c r="K27">
+        <v>15.4</v>
+      </c>
+      <c r="L27">
+        <v>12</v>
+      </c>
+      <c r="M27">
+        <v>2.486</v>
+      </c>
+      <c r="N27">
+        <v>9.513999999999999</v>
+      </c>
+      <c r="O27">
+        <v>1.4271</v>
+      </c>
+      <c r="P27">
+        <v>8.0869</v>
+      </c>
+      <c r="Q27">
+        <v>23.4869</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.135262326022966</v>
+      </c>
+      <c r="T27">
+        <v>1.352644225414353</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.15</v>
+      </c>
+      <c r="W27">
+        <v>0.04675</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.827031375703942</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1131009963439509</v>
+      </c>
+      <c r="C28">
+        <v>135.1230461312781</v>
+      </c>
+      <c r="D28">
+        <v>172.3310461312781</v>
+      </c>
+      <c r="E28">
+        <v>26.608</v>
+      </c>
+      <c r="F28">
+        <v>47.008</v>
+      </c>
+      <c r="G28">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H28">
+        <v>160.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>27.4</v>
+      </c>
+      <c r="K28">
+        <v>15.4</v>
+      </c>
+      <c r="L28">
+        <v>12</v>
+      </c>
+      <c r="M28">
+        <v>2.58544</v>
+      </c>
+      <c r="N28">
+        <v>9.41456</v>
+      </c>
+      <c r="O28">
+        <v>1.412184</v>
+      </c>
+      <c r="P28">
+        <v>8.002376</v>
+      </c>
+      <c r="Q28">
+        <v>23.402376</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1364135085729066</v>
+      </c>
+      <c r="T28">
+        <v>1.36878669774292</v>
+      </c>
+      <c r="U28">
+        <v>0.055</v>
+      </c>
+      <c r="V28">
+        <v>0.15</v>
+      </c>
+      <c r="W28">
+        <v>0.04675</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.641376322792252</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1139398481706773</v>
+      </c>
+      <c r="C29">
+        <v>131.3911639786214</v>
+      </c>
+      <c r="D29">
+        <v>170.4071639786214</v>
+      </c>
+      <c r="E29">
+        <v>28.41600000000001</v>
+      </c>
+      <c r="F29">
+        <v>48.81600000000001</v>
+      </c>
+      <c r="G29">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H29">
+        <v>160.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>27.4</v>
+      </c>
+      <c r="K29">
+        <v>15.4</v>
+      </c>
+      <c r="L29">
+        <v>12</v>
+      </c>
+      <c r="M29">
+        <v>2.870380800000001</v>
+      </c>
+      <c r="N29">
+        <v>9.129619199999999</v>
+      </c>
+      <c r="O29">
+        <v>1.36944288</v>
+      </c>
+      <c r="P29">
+        <v>7.760176319999998</v>
+      </c>
+      <c r="Q29">
+        <v>23.16017632</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1375962303707908</v>
+      </c>
+      <c r="T29">
+        <v>1.385371429587339</v>
+      </c>
+      <c r="U29">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.15</v>
+      </c>
+      <c r="W29">
+        <v>0.04998</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.180629970769034</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1139388999974037</v>
+      </c>
+      <c r="C30">
+        <v>129.5853143364057</v>
+      </c>
+      <c r="D30">
+        <v>170.4093143364057</v>
+      </c>
+      <c r="E30">
+        <v>30.22400000000001</v>
+      </c>
+      <c r="F30">
+        <v>50.62400000000001</v>
+      </c>
+      <c r="G30">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H30">
+        <v>160.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>27.4</v>
+      </c>
+      <c r="K30">
+        <v>15.4</v>
+      </c>
+      <c r="L30">
+        <v>12</v>
+      </c>
+      <c r="M30">
+        <v>2.976691200000001</v>
+      </c>
+      <c r="N30">
+        <v>9.023308799999999</v>
+      </c>
+      <c r="O30">
+        <v>1.35349632</v>
+      </c>
+      <c r="P30">
+        <v>7.669812479999999</v>
+      </c>
+      <c r="Q30">
+        <v>23.06981248</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1388118055519496</v>
+      </c>
+      <c r="T30">
+        <v>1.402416848427436</v>
+      </c>
+      <c r="U30">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V30">
+        <v>0.15</v>
+      </c>
+      <c r="W30">
+        <v>0.04998</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>4.031321757527283</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1149732518241301</v>
+      </c>
+      <c r="C31">
+        <v>125.4633369052989</v>
+      </c>
+      <c r="D31">
+        <v>168.0953369052989</v>
+      </c>
+      <c r="E31">
+        <v>32.032</v>
+      </c>
+      <c r="F31">
+        <v>52.432</v>
+      </c>
+      <c r="G31">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H31">
+        <v>160.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>27.4</v>
+      </c>
+      <c r="K31">
+        <v>15.4</v>
+      </c>
+      <c r="L31">
+        <v>12</v>
+      </c>
+      <c r="M31">
+        <v>3.303216</v>
+      </c>
+      <c r="N31">
+        <v>8.696783999999999</v>
+      </c>
+      <c r="O31">
+        <v>1.3045176</v>
+      </c>
+      <c r="P31">
+        <v>7.392266399999999</v>
+      </c>
+      <c r="Q31">
+        <v>22.7922664</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1400616222875072</v>
+      </c>
+      <c r="T31">
+        <v>1.419942419910915</v>
+      </c>
+      <c r="U31">
+        <v>0.063</v>
+      </c>
+      <c r="V31">
+        <v>0.15</v>
+      </c>
+      <c r="W31">
+        <v>0.05355</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.632823284944127</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1150080036508565</v>
+      </c>
+      <c r="C32">
+        <v>123.5786832765224</v>
+      </c>
+      <c r="D32">
+        <v>168.0186832765224</v>
+      </c>
+      <c r="E32">
+        <v>33.84</v>
+      </c>
+      <c r="F32">
+        <v>54.24</v>
+      </c>
+      <c r="G32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H32">
+        <v>160.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>27.4</v>
+      </c>
+      <c r="K32">
+        <v>15.4</v>
+      </c>
+      <c r="L32">
+        <v>12</v>
+      </c>
+      <c r="M32">
+        <v>3.41712</v>
+      </c>
+      <c r="N32">
+        <v>8.582879999999999</v>
+      </c>
+      <c r="O32">
+        <v>1.287432</v>
+      </c>
+      <c r="P32">
+        <v>7.295447999999999</v>
+      </c>
+      <c r="Q32">
+        <v>22.695448</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1413471480726521</v>
+      </c>
+      <c r="T32">
+        <v>1.437968722008209</v>
+      </c>
+      <c r="U32">
+        <v>0.063</v>
+      </c>
+      <c r="V32">
+        <v>0.15</v>
+      </c>
+      <c r="W32">
+        <v>0.05355</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.511729175445989</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1169136054775829</v>
+      </c>
+      <c r="C33">
+        <v>117.6718235731665</v>
+      </c>
+      <c r="D33">
+        <v>163.9198235731665</v>
+      </c>
+      <c r="E33">
+        <v>35.648</v>
+      </c>
+      <c r="F33">
+        <v>56.048</v>
+      </c>
+      <c r="G33">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H33">
+        <v>160.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>27.4</v>
+      </c>
+      <c r="K33">
+        <v>15.4</v>
+      </c>
+      <c r="L33">
+        <v>12</v>
+      </c>
+      <c r="M33">
+        <v>3.9289648</v>
+      </c>
+      <c r="N33">
+        <v>8.071035200000001</v>
+      </c>
+      <c r="O33">
+        <v>1.21065528</v>
+      </c>
+      <c r="P33">
+        <v>6.860379920000001</v>
+      </c>
+      <c r="Q33">
+        <v>22.26037992</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1426699354747578</v>
+      </c>
+      <c r="T33">
+        <v>1.456517525615568</v>
+      </c>
+      <c r="U33">
+        <v>0.0701</v>
+      </c>
+      <c r="V33">
+        <v>0.15</v>
+      </c>
+      <c r="W33">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>3.054239630754646</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1228023073043093</v>
+      </c>
+      <c r="C34">
+        <v>104.3727705832154</v>
+      </c>
+      <c r="D34">
+        <v>152.4287705832154</v>
+      </c>
+      <c r="E34">
+        <v>37.456</v>
+      </c>
+      <c r="F34">
+        <v>57.856</v>
+      </c>
+      <c r="G34">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H34">
+        <v>160.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>27.4</v>
+      </c>
+      <c r="K34">
+        <v>15.4</v>
+      </c>
+      <c r="L34">
+        <v>12</v>
+      </c>
+      <c r="M34">
+        <v>5.2880384</v>
+      </c>
+      <c r="N34">
+        <v>6.7119616</v>
+      </c>
+      <c r="O34">
+        <v>1.00679424</v>
+      </c>
+      <c r="P34">
+        <v>5.705167359999999</v>
+      </c>
+      <c r="Q34">
+        <v>21.10516736</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1440316283886902</v>
+      </c>
+      <c r="T34">
+        <v>1.475611882270204</v>
+      </c>
+      <c r="U34">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0.15</v>
+      </c>
+      <c r="W34">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.269272477295172</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1230784591310357</v>
+      </c>
+      <c r="C35">
+        <v>102.0653133805538</v>
+      </c>
+      <c r="D35">
+        <v>151.9293133805538</v>
+      </c>
+      <c r="E35">
+        <v>39.26400000000001</v>
+      </c>
+      <c r="F35">
+        <v>59.66400000000001</v>
+      </c>
+      <c r="G35">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H35">
+        <v>160.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>27.4</v>
+      </c>
+      <c r="K35">
+        <v>15.4</v>
+      </c>
+      <c r="L35">
+        <v>12</v>
+      </c>
+      <c r="M35">
+        <v>5.453289600000002</v>
+      </c>
+      <c r="N35">
+        <v>6.546710399999998</v>
+      </c>
+      <c r="O35">
+        <v>0.98200656</v>
+      </c>
+      <c r="P35">
+        <v>5.564703839999998</v>
+      </c>
+      <c r="Q35">
+        <v>20.96470384</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1454339688522921</v>
+      </c>
+      <c r="T35">
+        <v>1.4952762197205</v>
+      </c>
+      <c r="U35">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0.15</v>
+      </c>
+      <c r="W35">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.200506644649864</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1233546109577621</v>
+      </c>
+      <c r="C36">
+        <v>99.76111859060578</v>
+      </c>
+      <c r="D36">
+        <v>151.4331185906058</v>
+      </c>
+      <c r="E36">
+        <v>41.07200000000001</v>
+      </c>
+      <c r="F36">
+        <v>61.47200000000001</v>
+      </c>
+      <c r="G36">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H36">
+        <v>160.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>27.4</v>
+      </c>
+      <c r="K36">
+        <v>15.4</v>
+      </c>
+      <c r="L36">
+        <v>12</v>
+      </c>
+      <c r="M36">
+        <v>5.618540800000002</v>
+      </c>
+      <c r="N36">
+        <v>6.381459199999998</v>
+      </c>
+      <c r="O36">
+        <v>0.9572188799999999</v>
+      </c>
+      <c r="P36">
+        <v>5.424240319999998</v>
+      </c>
+      <c r="Q36">
+        <v>20.82424032</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1468788044814577</v>
+      </c>
+      <c r="T36">
+        <v>1.515536446184441</v>
+      </c>
+      <c r="U36">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0.15</v>
+      </c>
+      <c r="W36">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.135785860983691</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1236307627844885</v>
+      </c>
+      <c r="C37">
+        <v>97.46015435271588</v>
+      </c>
+      <c r="D37">
+        <v>150.9401543527159</v>
+      </c>
+      <c r="E37">
+        <v>42.88000000000001</v>
+      </c>
+      <c r="F37">
+        <v>63.28000000000001</v>
+      </c>
+      <c r="G37">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H37">
+        <v>160.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>27.4</v>
+      </c>
+      <c r="K37">
+        <v>15.4</v>
+      </c>
+      <c r="L37">
+        <v>12</v>
+      </c>
+      <c r="M37">
+        <v>5.783792000000001</v>
+      </c>
+      <c r="N37">
+        <v>6.216207999999999</v>
+      </c>
+      <c r="O37">
+        <v>0.9324312</v>
+      </c>
+      <c r="P37">
+        <v>5.283776799999999</v>
+      </c>
+      <c r="Q37">
+        <v>20.6837768</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1483680965915208</v>
+      </c>
+      <c r="T37">
+        <v>1.536420064231888</v>
+      </c>
+      <c r="U37">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.15</v>
+      </c>
+      <c r="W37">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.074763407812729</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1239069146112149</v>
+      </c>
+      <c r="C38">
+        <v>95.16238921975007</v>
+      </c>
+      <c r="D38">
+        <v>150.4503892197501</v>
+      </c>
+      <c r="E38">
+        <v>44.68800000000001</v>
+      </c>
+      <c r="F38">
+        <v>65.08800000000001</v>
+      </c>
+      <c r="G38">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H38">
+        <v>160.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>27.4</v>
+      </c>
+      <c r="K38">
+        <v>15.4</v>
+      </c>
+      <c r="L38">
+        <v>12</v>
+      </c>
+      <c r="M38">
+        <v>5.949043200000001</v>
+      </c>
+      <c r="N38">
+        <v>6.050956799999999</v>
+      </c>
+      <c r="O38">
+        <v>0.9076435199999999</v>
+      </c>
+      <c r="P38">
+        <v>5.143313279999999</v>
+      </c>
+      <c r="Q38">
+        <v>20.54331328</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1499039290800233</v>
+      </c>
+      <c r="T38">
+        <v>1.557956295343317</v>
+      </c>
+      <c r="U38">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.15</v>
+      </c>
+      <c r="W38">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>2.017131090929042</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1308190164379413</v>
+      </c>
+      <c r="C39">
+        <v>82.05315551379245</v>
+      </c>
+      <c r="D39">
+        <v>139.1491555137924</v>
+      </c>
+      <c r="E39">
+        <v>46.496</v>
+      </c>
+      <c r="F39">
+        <v>66.896</v>
+      </c>
+      <c r="G39">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H39">
+        <v>160.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>27.4</v>
+      </c>
+      <c r="K39">
+        <v>15.4</v>
+      </c>
+      <c r="L39">
+        <v>12</v>
+      </c>
+      <c r="M39">
+        <v>7.5258</v>
+      </c>
+      <c r="N39">
+        <v>4.4742</v>
+      </c>
+      <c r="O39">
+        <v>0.67113</v>
+      </c>
+      <c r="P39">
+        <v>3.80307</v>
+      </c>
+      <c r="Q39">
+        <v>19.20307</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1514885181554624</v>
+      </c>
+      <c r="T39">
+        <v>1.580176216331301</v>
+      </c>
+      <c r="U39">
+        <v>0.1125</v>
+      </c>
+      <c r="V39">
+        <v>0.15</v>
+      </c>
+      <c r="W39">
+        <v>0.095625</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>1.594514868851152</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1312745182646677</v>
+      </c>
+      <c r="C40">
+        <v>79.55974837987728</v>
+      </c>
+      <c r="D40">
+        <v>138.4637483798773</v>
+      </c>
+      <c r="E40">
+        <v>48.30400000000001</v>
+      </c>
+      <c r="F40">
+        <v>68.70400000000001</v>
+      </c>
+      <c r="G40">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H40">
+        <v>160.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>27.4</v>
+      </c>
+      <c r="K40">
+        <v>15.4</v>
+      </c>
+      <c r="L40">
+        <v>12</v>
+      </c>
+      <c r="M40">
+        <v>7.729200000000001</v>
+      </c>
+      <c r="N40">
+        <v>4.270799999999999</v>
+      </c>
+      <c r="O40">
+        <v>0.6406199999999999</v>
+      </c>
+      <c r="P40">
+        <v>3.630179999999999</v>
+      </c>
+      <c r="Q40">
+        <v>19.03018</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1531242230075286</v>
+      </c>
+      <c r="T40">
+        <v>1.603112908964058</v>
+      </c>
+      <c r="U40">
+        <v>0.1125</v>
+      </c>
+      <c r="V40">
+        <v>0.15</v>
+      </c>
+      <c r="W40">
+        <v>0.095625</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>1.552553951249806</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1317300200913941</v>
+      </c>
+      <c r="C41">
+        <v>77.07306037076694</v>
+      </c>
+      <c r="D41">
+        <v>137.7850603707669</v>
+      </c>
+      <c r="E41">
+        <v>50.112</v>
+      </c>
+      <c r="F41">
+        <v>70.512</v>
+      </c>
+      <c r="G41">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H41">
+        <v>160.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>27.4</v>
+      </c>
+      <c r="K41">
+        <v>15.4</v>
+      </c>
+      <c r="L41">
+        <v>12</v>
+      </c>
+      <c r="M41">
+        <v>7.9326</v>
+      </c>
+      <c r="N41">
+        <v>4.0674</v>
+      </c>
+      <c r="O41">
+        <v>0.6101100000000002</v>
+      </c>
+      <c r="P41">
+        <v>3.45729</v>
+      </c>
+      <c r="Q41">
+        <v>18.85729</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1548135575268756</v>
+      </c>
+      <c r="T41">
+        <v>1.626801624306085</v>
+      </c>
+      <c r="U41">
+        <v>0.1125</v>
+      </c>
+      <c r="V41">
+        <v>0.15</v>
+      </c>
+      <c r="W41">
+        <v>0.095625</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>1.512744875576734</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1633233457532858</v>
+      </c>
+      <c r="C42">
+        <v>40.30705103280962</v>
+      </c>
+      <c r="D42">
+        <v>102.8270510328096</v>
+      </c>
+      <c r="E42">
+        <v>51.92000000000001</v>
+      </c>
+      <c r="F42">
+        <v>72.32000000000001</v>
+      </c>
+      <c r="G42">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H42">
+        <v>160.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>27.4</v>
+      </c>
+      <c r="K42">
+        <v>15.4</v>
+      </c>
+      <c r="L42">
+        <v>12</v>
+      </c>
+      <c r="M42">
+        <v>14.218112</v>
+      </c>
+      <c r="N42">
+        <v>-2.218112000000001</v>
+      </c>
+      <c r="O42">
+        <v>-0.3327168000000003</v>
+      </c>
+      <c r="P42">
+        <v>-1.885395200000001</v>
+      </c>
+      <c r="Q42">
+        <v>13.5146048</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.157731829942792</v>
+      </c>
+      <c r="T42">
+        <v>1.667723137339427</v>
+      </c>
+      <c r="U42">
+        <v>0.1966</v>
+      </c>
+      <c r="V42">
+        <v>0.1265990871361824</v>
+      </c>
+      <c r="W42">
+        <v>0.1717106194690265</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.8439939142412156</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1649013457532859</v>
+      </c>
+      <c r="C43">
+        <v>37.21229960632417</v>
+      </c>
+      <c r="D43">
+        <v>101.5402996063242</v>
+      </c>
+      <c r="E43">
+        <v>53.72800000000002</v>
+      </c>
+      <c r="F43">
+        <v>74.12800000000001</v>
+      </c>
+      <c r="G43">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H43">
+        <v>160.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>27.4</v>
+      </c>
+      <c r="K43">
+        <v>15.4</v>
+      </c>
+      <c r="L43">
+        <v>12</v>
+      </c>
+      <c r="M43">
+        <v>14.5735648</v>
+      </c>
+      <c r="N43">
+        <v>-2.573564800000003</v>
+      </c>
+      <c r="O43">
+        <v>-0.3860347200000006</v>
+      </c>
+      <c r="P43">
+        <v>-2.187530080000003</v>
+      </c>
+      <c r="Q43">
+        <v>13.21246992</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.159747623670636</v>
+      </c>
+      <c r="T43">
+        <v>1.695989631192638</v>
+      </c>
+      <c r="U43">
+        <v>0.1966</v>
+      </c>
+      <c r="V43">
+        <v>0.1235113045231047</v>
+      </c>
+      <c r="W43">
+        <v>0.1723176775307576</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.8234086968206981</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1664793457532858</v>
+      </c>
+      <c r="C44">
+        <v>34.14935432262584</v>
+      </c>
+      <c r="D44">
+        <v>100.2853543226258</v>
+      </c>
+      <c r="E44">
+        <v>55.53600000000001</v>
+      </c>
+      <c r="F44">
+        <v>75.93600000000001</v>
+      </c>
+      <c r="G44">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H44">
+        <v>160.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>27.4</v>
+      </c>
+      <c r="K44">
+        <v>15.4</v>
+      </c>
+      <c r="L44">
+        <v>12</v>
+      </c>
+      <c r="M44">
+        <v>14.9290176</v>
+      </c>
+      <c r="N44">
+        <v>-2.929017600000002</v>
+      </c>
+      <c r="O44">
+        <v>-0.4393526400000003</v>
+      </c>
+      <c r="P44">
+        <v>-2.489664960000002</v>
+      </c>
+      <c r="Q44">
+        <v>12.91033504</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1618329275270262</v>
+      </c>
+      <c r="T44">
+        <v>1.725230831730442</v>
+      </c>
+      <c r="U44">
+        <v>0.1966</v>
+      </c>
+      <c r="V44">
+        <v>0.1205705591773165</v>
+      </c>
+      <c r="W44">
+        <v>0.1728958280657396</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.8038037278487767</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1757595629431563</v>
+      </c>
+      <c r="C45">
+        <v>25.54613791657358</v>
+      </c>
+      <c r="D45">
+        <v>93.49013791657359</v>
+      </c>
+      <c r="E45">
+        <v>57.344</v>
+      </c>
+      <c r="F45">
+        <v>77.744</v>
+      </c>
+      <c r="G45">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H45">
+        <v>160.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>27.4</v>
+      </c>
+      <c r="K45">
+        <v>15.4</v>
+      </c>
+      <c r="L45">
+        <v>12</v>
+      </c>
+      <c r="M45">
+        <v>16.6216672</v>
+      </c>
+      <c r="N45">
+        <v>-4.621667199999997</v>
+      </c>
+      <c r="O45">
+        <v>-0.6932500799999998</v>
+      </c>
+      <c r="P45">
+        <v>-3.928417119999998</v>
+      </c>
+      <c r="Q45">
+        <v>11.47158288</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1645286230799046</v>
+      </c>
+      <c r="T45">
+        <v>1.763031257797381</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.108292385976781</v>
+      </c>
+      <c r="W45">
+        <v>0.1906470878781642</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.7219492398452065</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1775095629431563</v>
+      </c>
+      <c r="C46">
+        <v>22.55863927291446</v>
+      </c>
+      <c r="D46">
+        <v>92.31063927291447</v>
+      </c>
+      <c r="E46">
+        <v>59.15200000000001</v>
+      </c>
+      <c r="F46">
+        <v>79.55200000000001</v>
+      </c>
+      <c r="G46">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H46">
+        <v>160.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>27.4</v>
+      </c>
+      <c r="K46">
+        <v>15.4</v>
+      </c>
+      <c r="L46">
+        <v>12</v>
+      </c>
+      <c r="M46">
+        <v>17.0082176</v>
+      </c>
+      <c r="N46">
+        <v>-5.008217600000002</v>
+      </c>
+      <c r="O46">
+        <v>-0.7512326400000003</v>
+      </c>
+      <c r="P46">
+        <v>-4.256984960000001</v>
+      </c>
+      <c r="Q46">
+        <v>11.14301504</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1667737770634743</v>
+      </c>
+      <c r="T46">
+        <v>1.794513958829477</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.1058311953863996</v>
+      </c>
+      <c r="W46">
+        <v>0.1911732904263878</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.7055413025759971</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1792595629431563</v>
+      </c>
+      <c r="C47">
+        <v>19.60053161671324</v>
+      </c>
+      <c r="D47">
+        <v>91.16053161671326</v>
+      </c>
+      <c r="E47">
+        <v>60.96000000000002</v>
+      </c>
+      <c r="F47">
+        <v>81.36000000000001</v>
+      </c>
+      <c r="G47">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H47">
+        <v>160.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>27.4</v>
+      </c>
+      <c r="K47">
+        <v>15.4</v>
+      </c>
+      <c r="L47">
+        <v>12</v>
+      </c>
+      <c r="M47">
+        <v>17.394768</v>
+      </c>
+      <c r="N47">
+        <v>-5.394768000000003</v>
+      </c>
+      <c r="O47">
+        <v>-0.8092152000000005</v>
+      </c>
+      <c r="P47">
+        <v>-4.585552800000002</v>
+      </c>
+      <c r="Q47">
+        <v>10.8144472</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.169100573010083</v>
+      </c>
+      <c r="T47">
+        <v>1.827141485353649</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.1034793910444796</v>
+      </c>
+      <c r="W47">
+        <v>0.1916761061946902</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.6898626069631971</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1810095629431563</v>
+      </c>
+      <c r="C48">
+        <v>16.67072991064221</v>
+      </c>
+      <c r="D48">
+        <v>90.03872991064222</v>
+      </c>
+      <c r="E48">
+        <v>62.76800000000001</v>
+      </c>
+      <c r="F48">
+        <v>83.16800000000001</v>
+      </c>
+      <c r="G48">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H48">
+        <v>160.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>27.4</v>
+      </c>
+      <c r="K48">
+        <v>15.4</v>
+      </c>
+      <c r="L48">
+        <v>12</v>
+      </c>
+      <c r="M48">
+        <v>17.7813184</v>
+      </c>
+      <c r="N48">
+        <v>-5.7813184</v>
+      </c>
+      <c r="O48">
+        <v>-0.8671977600000002</v>
+      </c>
+      <c r="P48">
+        <v>-4.91412064</v>
+      </c>
+      <c r="Q48">
+        <v>10.48587936</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1715135465843438</v>
+      </c>
+      <c r="T48">
+        <v>1.860977438786124</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1012298390652518</v>
+      </c>
+      <c r="W48">
+        <v>0.1921570604078492</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.6748655937683451</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1827595629431563</v>
+      </c>
+      <c r="C49">
+        <v>13.76820187705933</v>
+      </c>
+      <c r="D49">
+        <v>88.94420187705934</v>
+      </c>
+      <c r="E49">
+        <v>64.57600000000002</v>
+      </c>
+      <c r="F49">
+        <v>84.97600000000001</v>
+      </c>
+      <c r="G49">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H49">
+        <v>160.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>27.4</v>
+      </c>
+      <c r="K49">
+        <v>15.4</v>
+      </c>
+      <c r="L49">
+        <v>12</v>
+      </c>
+      <c r="M49">
+        <v>18.1678688</v>
+      </c>
+      <c r="N49">
+        <v>-6.167868800000001</v>
+      </c>
+      <c r="O49">
+        <v>-0.9251803200000003</v>
+      </c>
+      <c r="P49">
+        <v>-5.242688480000001</v>
+      </c>
+      <c r="Q49">
+        <v>10.15731152</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1740175757651804</v>
+      </c>
+      <c r="T49">
+        <v>1.896090220650014</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.09907601270216131</v>
+      </c>
+      <c r="W49">
+        <v>0.1926175484842779</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.6605067513477421</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1845095629431562</v>
+      </c>
+      <c r="C50">
+        <v>10.89196482973819</v>
+      </c>
+      <c r="D50">
+        <v>87.87596482973819</v>
+      </c>
+      <c r="E50">
+        <v>66.38400000000001</v>
+      </c>
+      <c r="F50">
+        <v>86.78400000000001</v>
+      </c>
+      <c r="G50">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H50">
+        <v>160.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>27.4</v>
+      </c>
+      <c r="K50">
+        <v>15.4</v>
+      </c>
+      <c r="L50">
+        <v>12</v>
+      </c>
+      <c r="M50">
+        <v>18.5544192</v>
+      </c>
+      <c r="N50">
+        <v>-6.554419200000002</v>
+      </c>
+      <c r="O50">
+        <v>-0.9831628800000004</v>
+      </c>
+      <c r="P50">
+        <v>-5.571256320000002</v>
+      </c>
+      <c r="Q50">
+        <v>9.828743679999997</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1766179137606647</v>
+      </c>
+      <c r="T50">
+        <v>1.932553494124052</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.09701192910419962</v>
+      </c>
+      <c r="W50">
+        <v>0.1930588495575221</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.6467461940279973</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1862595629431562</v>
+      </c>
+      <c r="C51">
+        <v>8.041082731197562</v>
+      </c>
+      <c r="D51">
+        <v>86.83308273119756</v>
+      </c>
+      <c r="E51">
+        <v>68.19200000000001</v>
+      </c>
+      <c r="F51">
+        <v>88.592</v>
+      </c>
+      <c r="G51">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H51">
+        <v>160.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>27.4</v>
+      </c>
+      <c r="K51">
+        <v>15.4</v>
+      </c>
+      <c r="L51">
+        <v>12</v>
+      </c>
+      <c r="M51">
+        <v>18.9409696</v>
+      </c>
+      <c r="N51">
+        <v>-6.940969599999999</v>
+      </c>
+      <c r="O51">
+        <v>-1.04114544</v>
+      </c>
+      <c r="P51">
+        <v>-5.899824159999999</v>
+      </c>
+      <c r="Q51">
+        <v>9.500175840000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1793202257951875</v>
+      </c>
+      <c r="T51">
+        <v>1.97044669989119</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.09503209381635881</v>
+      </c>
+      <c r="W51">
+        <v>0.1934821383420625</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.6335472921090587</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1880095629431562</v>
+      </c>
+      <c r="C52">
+        <v>5.21466345710931</v>
+      </c>
+      <c r="D52">
+        <v>85.81466345710932</v>
+      </c>
+      <c r="E52">
+        <v>70</v>
+      </c>
+      <c r="F52">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="G52">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H52">
+        <v>160.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>27.4</v>
+      </c>
+      <c r="K52">
+        <v>15.4</v>
+      </c>
+      <c r="L52">
+        <v>12</v>
+      </c>
+      <c r="M52">
+        <v>19.32752</v>
+      </c>
+      <c r="N52">
+        <v>-7.32752</v>
+      </c>
+      <c r="O52">
+        <v>-1.099128</v>
+      </c>
+      <c r="P52">
+        <v>-6.228391999999999</v>
+      </c>
+      <c r="Q52">
+        <v>9.171607999999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1821306303110913</v>
+      </c>
+      <c r="T52">
+        <v>2.009855633889014</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.09313145194003164</v>
+      </c>
+      <c r="W52">
+        <v>0.1938884955752212</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.6208763462668775</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1897595629431562</v>
+      </c>
+      <c r="C53">
+        <v>2.411856250980279</v>
+      </c>
+      <c r="D53">
+        <v>84.81985625098029</v>
+      </c>
+      <c r="E53">
+        <v>71.80800000000002</v>
+      </c>
+      <c r="F53">
+        <v>92.20800000000001</v>
+      </c>
+      <c r="G53">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H53">
+        <v>160.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>27.4</v>
+      </c>
+      <c r="K53">
+        <v>15.4</v>
+      </c>
+      <c r="L53">
+        <v>12</v>
+      </c>
+      <c r="M53">
+        <v>19.7140704</v>
+      </c>
+      <c r="N53">
+        <v>-7.714070400000001</v>
+      </c>
+      <c r="O53">
+        <v>-1.15711056</v>
+      </c>
+      <c r="P53">
+        <v>-6.55695984</v>
+      </c>
+      <c r="Q53">
+        <v>8.843040159999997</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1850557452153992</v>
+      </c>
+      <c r="T53">
+        <v>2.050873095805116</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.09130534503924671</v>
+      </c>
+      <c r="W53">
+        <v>0.1942789172306091</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.6087023002616445</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1915095629431562</v>
+      </c>
+      <c r="C54">
+        <v>-0.3681506461547031</v>
+      </c>
+      <c r="D54">
+        <v>83.84784935384531</v>
+      </c>
+      <c r="E54">
+        <v>73.61600000000001</v>
+      </c>
+      <c r="F54">
+        <v>94.01600000000001</v>
+      </c>
+      <c r="G54">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H54">
+        <v>160.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>27.4</v>
+      </c>
+      <c r="K54">
+        <v>15.4</v>
+      </c>
+      <c r="L54">
+        <v>12</v>
+      </c>
+      <c r="M54">
+        <v>20.1006208</v>
+      </c>
+      <c r="N54">
+        <v>-8.100620800000002</v>
+      </c>
+      <c r="O54">
+        <v>-1.21509312</v>
+      </c>
+      <c r="P54">
+        <v>-6.885527680000001</v>
+      </c>
+      <c r="Q54">
+        <v>8.514472319999998</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1881027399073867</v>
+      </c>
+      <c r="T54">
+        <v>2.09359961863439</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.08954947301926118</v>
+      </c>
+      <c r="W54">
+        <v>0.194654322668482</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5969964867950744</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1932595629431562</v>
+      </c>
+      <c r="C55">
+        <v>-3.126132204908899</v>
+      </c>
+      <c r="D55">
+        <v>82.89786779509112</v>
+      </c>
+      <c r="E55">
+        <v>75.42400000000001</v>
+      </c>
+      <c r="F55">
+        <v>95.82400000000001</v>
+      </c>
+      <c r="G55">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H55">
+        <v>160.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>27.4</v>
+      </c>
+      <c r="K55">
+        <v>15.4</v>
+      </c>
+      <c r="L55">
+        <v>12</v>
+      </c>
+      <c r="M55">
+        <v>20.4871712</v>
+      </c>
+      <c r="N55">
+        <v>-8.487171200000002</v>
+      </c>
+      <c r="O55">
+        <v>-1.27307568</v>
+      </c>
+      <c r="P55">
+        <v>-7.214095520000002</v>
+      </c>
+      <c r="Q55">
+        <v>8.185904479999998</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1912793939479694</v>
+      </c>
+      <c r="T55">
+        <v>2.138144291371292</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.08785986032078455</v>
+      </c>
+      <c r="W55">
+        <v>0.1950155618634163</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5857324021385636</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1950095629431562</v>
+      </c>
+      <c r="C56">
+        <v>-5.862828668224665</v>
+      </c>
+      <c r="D56">
+        <v>81.96917133177536</v>
+      </c>
+      <c r="E56">
+        <v>77.23200000000003</v>
+      </c>
+      <c r="F56">
+        <v>97.63200000000002</v>
+      </c>
+      <c r="G56">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H56">
+        <v>160.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>27.4</v>
+      </c>
+      <c r="K56">
+        <v>15.4</v>
+      </c>
+      <c r="L56">
+        <v>12</v>
+      </c>
+      <c r="M56">
+        <v>20.8737216</v>
+      </c>
+      <c r="N56">
+        <v>-8.873721600000003</v>
+      </c>
+      <c r="O56">
+        <v>-1.331058240000001</v>
+      </c>
+      <c r="P56">
+        <v>-7.542663360000002</v>
+      </c>
+      <c r="Q56">
+        <v>7.857336639999996</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.194594163381621</v>
+      </c>
+      <c r="T56">
+        <v>2.184625689009799</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.08623282587039965</v>
+      </c>
+      <c r="W56">
+        <v>0.1953634218289085</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5748855058026643</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1967595629431562</v>
+      </c>
+      <c r="C57">
+        <v>-8.57894747507541</v>
+      </c>
+      <c r="D57">
+        <v>81.06105252492461</v>
+      </c>
+      <c r="E57">
+        <v>79.04000000000002</v>
+      </c>
+      <c r="F57">
+        <v>99.44000000000001</v>
+      </c>
+      <c r="G57">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H57">
+        <v>160.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>27.4</v>
+      </c>
+      <c r="K57">
+        <v>15.4</v>
+      </c>
+      <c r="L57">
+        <v>12</v>
+      </c>
+      <c r="M57">
+        <v>21.260272</v>
+      </c>
+      <c r="N57">
+        <v>-9.260272000000001</v>
+      </c>
+      <c r="O57">
+        <v>-1.3890408</v>
+      </c>
+      <c r="P57">
+        <v>-7.8712312</v>
+      </c>
+      <c r="Q57">
+        <v>7.528768799999998</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1980562559012125</v>
+      </c>
+      <c r="T57">
+        <v>2.233172926543349</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.08466495630911967</v>
+      </c>
+      <c r="W57">
+        <v>0.1956986323411102</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5644330420607977</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1985095629431562</v>
+      </c>
+      <c r="C58">
+        <v>-11.27516505769512</v>
+      </c>
+      <c r="D58">
+        <v>80.1728349423049</v>
+      </c>
+      <c r="E58">
+        <v>80.84800000000001</v>
+      </c>
+      <c r="F58">
+        <v>101.248</v>
+      </c>
+      <c r="G58">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H58">
+        <v>160.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>27.4</v>
+      </c>
+      <c r="K58">
+        <v>15.4</v>
+      </c>
+      <c r="L58">
+        <v>12</v>
+      </c>
+      <c r="M58">
+        <v>21.6468224</v>
+      </c>
+      <c r="N58">
+        <v>-9.646822400000001</v>
+      </c>
+      <c r="O58">
+        <v>-1.44702336</v>
+      </c>
+      <c r="P58">
+        <v>-8.19979904</v>
+      </c>
+      <c r="Q58">
+        <v>7.200200959999998</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2016757162626037</v>
+      </c>
+      <c r="T58">
+        <v>2.283926856692062</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.08315308208931396</v>
+      </c>
+      <c r="W58">
+        <v>0.1960218710493047</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5543538805954262</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2002595629431562</v>
+      </c>
+      <c r="C59">
+        <v>-13.9521285219306</v>
+      </c>
+      <c r="D59">
+        <v>79.30387147806941</v>
+      </c>
+      <c r="E59">
+        <v>82.65600000000001</v>
+      </c>
+      <c r="F59">
+        <v>103.056</v>
+      </c>
+      <c r="G59">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H59">
+        <v>160.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>27.4</v>
+      </c>
+      <c r="K59">
+        <v>15.4</v>
+      </c>
+      <c r="L59">
+        <v>12</v>
+      </c>
+      <c r="M59">
+        <v>22.0333728</v>
+      </c>
+      <c r="N59">
+        <v>-10.0333728</v>
+      </c>
+      <c r="O59">
+        <v>-1.505005920000001</v>
+      </c>
+      <c r="P59">
+        <v>-8.528366880000002</v>
+      </c>
+      <c r="Q59">
+        <v>6.871633119999997</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.205463523617548</v>
+      </c>
+      <c r="T59">
+        <v>2.337041434754668</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.08169425608774704</v>
+      </c>
+      <c r="W59">
+        <v>0.1963337680484397</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5446283739183135</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2020095629431563</v>
+      </c>
+      <c r="C60">
+        <v>-16.61045721948956</v>
+      </c>
+      <c r="D60">
+        <v>78.45354278051045</v>
+      </c>
+      <c r="E60">
+        <v>84.464</v>
+      </c>
+      <c r="F60">
+        <v>104.864</v>
+      </c>
+      <c r="G60">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H60">
+        <v>160.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>27.4</v>
+      </c>
+      <c r="K60">
+        <v>15.4</v>
+      </c>
+      <c r="L60">
+        <v>12</v>
+      </c>
+      <c r="M60">
+        <v>22.4199232</v>
+      </c>
+      <c r="N60">
+        <v>-10.4199232</v>
+      </c>
+      <c r="O60">
+        <v>-1.56298848</v>
+      </c>
+      <c r="P60">
+        <v>-8.85693472</v>
+      </c>
+      <c r="Q60">
+        <v>6.543065279999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2094317027512991</v>
+      </c>
+      <c r="T60">
+        <v>2.392685278439303</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.08028573443106177</v>
+      </c>
+      <c r="W60">
+        <v>0.196634909978639</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5352382295404117</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2037595629431563</v>
+      </c>
+      <c r="C61">
+        <v>-19.25074422011167</v>
+      </c>
+      <c r="D61">
+        <v>77.62125577988833</v>
+      </c>
+      <c r="E61">
+        <v>86.27199999999999</v>
+      </c>
+      <c r="F61">
+        <v>106.672</v>
+      </c>
+      <c r="G61">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H61">
+        <v>160.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>27.4</v>
+      </c>
+      <c r="K61">
+        <v>15.4</v>
+      </c>
+      <c r="L61">
+        <v>12</v>
+      </c>
+      <c r="M61">
+        <v>22.8064736</v>
+      </c>
+      <c r="N61">
+        <v>-10.8064736</v>
+      </c>
+      <c r="O61">
+        <v>-1.62097104</v>
+      </c>
+      <c r="P61">
+        <v>-9.185502559999996</v>
+      </c>
+      <c r="Q61">
+        <v>6.214497440000002</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2135934515988918</v>
+      </c>
+      <c r="T61">
+        <v>2.451043455962213</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.07892495927121326</v>
+      </c>
+      <c r="W61">
+        <v>0.1969258437078146</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.5261663951414217</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2055095629431563</v>
+      </c>
+      <c r="C62">
+        <v>-21.87355769101688</v>
+      </c>
+      <c r="D62">
+        <v>76.80644230898312</v>
+      </c>
+      <c r="E62">
+        <v>88.08000000000001</v>
+      </c>
+      <c r="F62">
+        <v>108.48</v>
+      </c>
+      <c r="G62">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H62">
+        <v>160.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>27.4</v>
+      </c>
+      <c r="K62">
+        <v>15.4</v>
+      </c>
+      <c r="L62">
+        <v>12</v>
+      </c>
+      <c r="M62">
+        <v>23.193024</v>
+      </c>
+      <c r="N62">
+        <v>-11.193024</v>
+      </c>
+      <c r="O62">
+        <v>-1.6789536</v>
+      </c>
+      <c r="P62">
+        <v>-9.514070400000001</v>
+      </c>
+      <c r="Q62">
+        <v>5.885929599999997</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2179632878888641</v>
+      </c>
+      <c r="T62">
+        <v>2.512319542361268</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.0776095432833597</v>
+      </c>
+      <c r="W62">
+        <v>0.1972070796460177</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5173969552223978</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2072595629431562</v>
+      </c>
+      <c r="C63">
+        <v>-24.4794421903734</v>
+      </c>
+      <c r="D63">
+        <v>76.00855780962661</v>
+      </c>
+      <c r="E63">
+        <v>89.88800000000001</v>
+      </c>
+      <c r="F63">
+        <v>110.288</v>
+      </c>
+      <c r="G63">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H63">
+        <v>160.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>27.4</v>
+      </c>
+      <c r="K63">
+        <v>15.4</v>
+      </c>
+      <c r="L63">
+        <v>12</v>
+      </c>
+      <c r="M63">
+        <v>23.5795744</v>
+      </c>
+      <c r="N63">
+        <v>-11.5795744</v>
+      </c>
+      <c r="O63">
+        <v>-1.736936160000001</v>
+      </c>
+      <c r="P63">
+        <v>-9.842638240000001</v>
+      </c>
+      <c r="Q63">
+        <v>5.557361759999997</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2225572183475529</v>
+      </c>
+      <c r="T63">
+        <v>2.576737992165403</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.07633725568855051</v>
+      </c>
+      <c r="W63">
+        <v>0.1974790947337879</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.50891503792367</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2090095629431563</v>
+      </c>
+      <c r="C64">
+        <v>-27.06891988097338</v>
+      </c>
+      <c r="D64">
+        <v>75.22708011902662</v>
+      </c>
+      <c r="E64">
+        <v>91.696</v>
+      </c>
+      <c r="F64">
+        <v>112.096</v>
+      </c>
+      <c r="G64">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H64">
+        <v>160.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>27.4</v>
+      </c>
+      <c r="K64">
+        <v>15.4</v>
+      </c>
+      <c r="L64">
+        <v>12</v>
+      </c>
+      <c r="M64">
+        <v>23.9661248</v>
+      </c>
+      <c r="N64">
+        <v>-11.9661248</v>
+      </c>
+      <c r="O64">
+        <v>-1.79491872</v>
+      </c>
+      <c r="P64">
+        <v>-10.17120608</v>
+      </c>
+      <c r="Q64">
+        <v>5.228793919999999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2273929346198569</v>
+      </c>
+      <c r="T64">
+        <v>2.644546886696072</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.07510600962905778</v>
+      </c>
+      <c r="W64">
+        <v>0.1977423351413074</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.5007067308603851</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2268759923499317</v>
+      </c>
+      <c r="C65">
+        <v>-36.02317655962342</v>
+      </c>
+      <c r="D65">
+        <v>68.08082344037659</v>
+      </c>
+      <c r="E65">
+        <v>93.50400000000002</v>
+      </c>
+      <c r="F65">
+        <v>113.904</v>
+      </c>
+      <c r="G65">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H65">
+        <v>160.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>27.4</v>
+      </c>
+      <c r="K65">
+        <v>15.4</v>
+      </c>
+      <c r="L65">
+        <v>12</v>
+      </c>
+      <c r="M65">
+        <v>27.2002752</v>
+      </c>
+      <c r="N65">
+        <v>-15.2002752</v>
+      </c>
+      <c r="O65">
+        <v>-2.280041280000001</v>
+      </c>
+      <c r="P65">
+        <v>-12.92023392</v>
+      </c>
+      <c r="Q65">
+        <v>2.479766079999996</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2334803907089758</v>
+      </c>
+      <c r="T65">
+        <v>2.729908319142245</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.06617580104483649</v>
+      </c>
+      <c r="W65">
+        <v>0.2229972187104931</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.4411720069655766</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2288759923499317</v>
+      </c>
+      <c r="C66">
+        <v>-38.54753029371348</v>
+      </c>
+      <c r="D66">
+        <v>67.36446970628653</v>
+      </c>
+      <c r="E66">
+        <v>95.31200000000001</v>
+      </c>
+      <c r="F66">
+        <v>115.712</v>
+      </c>
+      <c r="G66">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H66">
+        <v>160.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>27.4</v>
+      </c>
+      <c r="K66">
+        <v>15.4</v>
+      </c>
+      <c r="L66">
+        <v>12</v>
+      </c>
+      <c r="M66">
+        <v>27.6320256</v>
+      </c>
+      <c r="N66">
+        <v>-15.6320256</v>
+      </c>
+      <c r="O66">
+        <v>-2.344803840000001</v>
+      </c>
+      <c r="P66">
+        <v>-13.28722176</v>
+      </c>
+      <c r="Q66">
+        <v>2.112778239999997</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2388881793397807</v>
+      </c>
+      <c r="T66">
+        <v>2.805739105785085</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.06514180415351092</v>
+      </c>
+      <c r="W66">
+        <v>0.2232441371681416</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.4342786943567394</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2308759923499317</v>
+      </c>
+      <c r="C67">
+        <v>-41.05696589617608</v>
+      </c>
+      <c r="D67">
+        <v>66.66303410382393</v>
+      </c>
+      <c r="E67">
+        <v>97.12</v>
+      </c>
+      <c r="F67">
+        <v>117.52</v>
+      </c>
+      <c r="G67">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H67">
+        <v>160.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>27.4</v>
+      </c>
+      <c r="K67">
+        <v>15.4</v>
+      </c>
+      <c r="L67">
+        <v>12</v>
+      </c>
+      <c r="M67">
+        <v>28.063776</v>
+      </c>
+      <c r="N67">
+        <v>-16.063776</v>
+      </c>
+      <c r="O67">
+        <v>-2.409566400000001</v>
+      </c>
+      <c r="P67">
+        <v>-13.6542096</v>
+      </c>
+      <c r="Q67">
+        <v>1.745790399999995</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2446049844637744</v>
+      </c>
+      <c r="T67">
+        <v>2.885903080236087</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.0641396225511492</v>
+      </c>
+      <c r="W67">
+        <v>0.2234834581347856</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.427597483674328</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2328759923499317</v>
+      </c>
+      <c r="C68">
+        <v>-43.55194457186541</v>
+      </c>
+      <c r="D68">
+        <v>65.97605542813461</v>
+      </c>
+      <c r="E68">
+        <v>98.92800000000003</v>
+      </c>
+      <c r="F68">
+        <v>119.328</v>
+      </c>
+      <c r="G68">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H68">
+        <v>160.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>27.4</v>
+      </c>
+      <c r="K68">
+        <v>15.4</v>
+      </c>
+      <c r="L68">
+        <v>12</v>
+      </c>
+      <c r="M68">
+        <v>28.49552640000001</v>
+      </c>
+      <c r="N68">
+        <v>-16.49552640000001</v>
+      </c>
+      <c r="O68">
+        <v>-2.474328960000001</v>
+      </c>
+      <c r="P68">
+        <v>-14.02119744000001</v>
+      </c>
+      <c r="Q68">
+        <v>1.378802559999993</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2506580722421207</v>
+      </c>
+      <c r="T68">
+        <v>2.970782582595972</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.06316781008825301</v>
+      </c>
+      <c r="W68">
+        <v>0.2237155269509252</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.4211187339216866</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2348759923499317</v>
+      </c>
+      <c r="C69">
+        <v>-46.0329087082436</v>
+      </c>
+      <c r="D69">
+        <v>65.30309129175642</v>
+      </c>
+      <c r="E69">
+        <v>100.736</v>
+      </c>
+      <c r="F69">
+        <v>121.136</v>
+      </c>
+      <c r="G69">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H69">
+        <v>160.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>27.4</v>
+      </c>
+      <c r="K69">
+        <v>15.4</v>
+      </c>
+      <c r="L69">
+        <v>12</v>
+      </c>
+      <c r="M69">
+        <v>28.9272768</v>
+      </c>
+      <c r="N69">
+        <v>-16.9272768</v>
+      </c>
+      <c r="O69">
+        <v>-2.539091520000001</v>
+      </c>
+      <c r="P69">
+        <v>-14.38818528</v>
+      </c>
+      <c r="Q69">
+        <v>1.011814719999995</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2570780138252153</v>
+      </c>
+      <c r="T69">
+        <v>3.060806297220092</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.06222500695260744</v>
+      </c>
+      <c r="W69">
+        <v>0.2239406683397173</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.4148333796840495</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2368759923499317</v>
+      </c>
+      <c r="C70">
+        <v>-48.50028282538939</v>
+      </c>
+      <c r="D70">
+        <v>64.64371717461063</v>
+      </c>
+      <c r="E70">
+        <v>102.544</v>
+      </c>
+      <c r="F70">
+        <v>122.944</v>
+      </c>
+      <c r="G70">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H70">
+        <v>160.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>27.4</v>
+      </c>
+      <c r="K70">
+        <v>15.4</v>
+      </c>
+      <c r="L70">
+        <v>12</v>
+      </c>
+      <c r="M70">
+        <v>29.35902720000001</v>
+      </c>
+      <c r="N70">
+        <v>-17.35902720000001</v>
+      </c>
+      <c r="O70">
+        <v>-2.603854080000001</v>
+      </c>
+      <c r="P70">
+        <v>-14.75517312000001</v>
+      </c>
+      <c r="Q70">
+        <v>0.644826879999993</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2638992017572533</v>
+      </c>
+      <c r="T70">
+        <v>3.15645649400822</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.06130993332095144</v>
+      </c>
+      <c r="W70">
+        <v>0.2241591879229568</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.408732888806343</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2388759923499317</v>
+      </c>
+      <c r="C71">
+        <v>-50.95447446902797</v>
+      </c>
+      <c r="D71">
+        <v>63.99752553097206</v>
+      </c>
+      <c r="E71">
+        <v>104.352</v>
+      </c>
+      <c r="F71">
+        <v>124.752</v>
+      </c>
+      <c r="G71">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H71">
+        <v>160.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>27.4</v>
+      </c>
+      <c r="K71">
+        <v>15.4</v>
+      </c>
+      <c r="L71">
+        <v>12</v>
+      </c>
+      <c r="M71">
+        <v>29.79077760000001</v>
+      </c>
+      <c r="N71">
+        <v>-17.79077760000001</v>
+      </c>
+      <c r="O71">
+        <v>-2.668616640000001</v>
+      </c>
+      <c r="P71">
+        <v>-15.12216096</v>
+      </c>
+      <c r="Q71">
+        <v>0.2778390399999946</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2711604663300679</v>
+      </c>
+      <c r="T71">
+        <v>3.258277671234292</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.06042138356267679</v>
+      </c>
+      <c r="W71">
+        <v>0.2243713736052328</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.4028092237511786</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2408759923499317</v>
+      </c>
+      <c r="C72">
+        <v>-53.3958750505295</v>
+      </c>
+      <c r="D72">
+        <v>63.36412494947052</v>
+      </c>
+      <c r="E72">
+        <v>106.16</v>
+      </c>
+      <c r="F72">
+        <v>126.56</v>
+      </c>
+      <c r="G72">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H72">
+        <v>160.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>27.4</v>
+      </c>
+      <c r="K72">
+        <v>15.4</v>
+      </c>
+      <c r="L72">
+        <v>12</v>
+      </c>
+      <c r="M72">
+        <v>30.222528</v>
+      </c>
+      <c r="N72">
+        <v>-18.222528</v>
+      </c>
+      <c r="O72">
+        <v>-2.733379200000001</v>
+      </c>
+      <c r="P72">
+        <v>-15.4891488</v>
+      </c>
+      <c r="Q72">
+        <v>-0.0891488000000038</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2789058152077368</v>
+      </c>
+      <c r="T72">
+        <v>3.366886926942102</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.05955822094035283</v>
+      </c>
+      <c r="W72">
+        <v>0.2245774968394438</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3970548062690189</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2428759923499317</v>
+      </c>
+      <c r="C73">
+        <v>-55.82486063751433</v>
+      </c>
+      <c r="D73">
+        <v>62.74313936248566</v>
+      </c>
+      <c r="E73">
+        <v>107.968</v>
+      </c>
+      <c r="F73">
+        <v>128.368</v>
+      </c>
+      <c r="G73">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H73">
+        <v>160.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>27.4</v>
+      </c>
+      <c r="K73">
+        <v>15.4</v>
+      </c>
+      <c r="L73">
+        <v>12</v>
+      </c>
+      <c r="M73">
+        <v>30.6542784</v>
+      </c>
+      <c r="N73">
+        <v>-18.6542784</v>
+      </c>
+      <c r="O73">
+        <v>-2.79814176</v>
+      </c>
+      <c r="P73">
+        <v>-15.85613664</v>
+      </c>
+      <c r="Q73">
+        <v>-0.4561366400000004</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2871853260769691</v>
+      </c>
+      <c r="T73">
+        <v>3.482986476147001</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.05871937275809436</v>
+      </c>
+      <c r="W73">
+        <v>0.2247778137853671</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3914624850539623</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2448759923499317</v>
+      </c>
+      <c r="C74">
+        <v>-58.24179269842074</v>
+      </c>
+      <c r="D74">
+        <v>62.13420730157927</v>
+      </c>
+      <c r="E74">
+        <v>109.776</v>
+      </c>
+      <c r="F74">
+        <v>130.176</v>
+      </c>
+      <c r="G74">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H74">
+        <v>160.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>27.4</v>
+      </c>
+      <c r="K74">
+        <v>15.4</v>
+      </c>
+      <c r="L74">
+        <v>12</v>
+      </c>
+      <c r="M74">
+        <v>31.0860288</v>
+      </c>
+      <c r="N74">
+        <v>-19.0860288</v>
+      </c>
+      <c r="O74">
+        <v>-2.862904320000001</v>
+      </c>
+      <c r="P74">
+        <v>-16.22312448</v>
+      </c>
+      <c r="Q74">
+        <v>-0.8231244800000042</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.296056230579718</v>
+      </c>
+      <c r="T74">
+        <v>3.607378850295108</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.05790382591423193</v>
+      </c>
+      <c r="W74">
+        <v>0.2249725663716814</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3860255060948794</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2468759923499317</v>
+      </c>
+      <c r="C75">
+        <v>-60.647018804132</v>
+      </c>
+      <c r="D75">
+        <v>61.53698119586801</v>
+      </c>
+      <c r="E75">
+        <v>111.584</v>
+      </c>
+      <c r="F75">
+        <v>131.984</v>
+      </c>
+      <c r="G75">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H75">
+        <v>160.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>27.4</v>
+      </c>
+      <c r="K75">
+        <v>15.4</v>
+      </c>
+      <c r="L75">
+        <v>12</v>
+      </c>
+      <c r="M75">
+        <v>31.5177792</v>
+      </c>
+      <c r="N75">
+        <v>-19.5177792</v>
+      </c>
+      <c r="O75">
+        <v>-2.927666880000001</v>
+      </c>
+      <c r="P75">
+        <v>-16.59011232</v>
+      </c>
+      <c r="Q75">
+        <v>-1.190112320000004</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3055842391197076</v>
+      </c>
+      <c r="T75">
+        <v>3.740985474380112</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.05711062281951643</v>
+      </c>
+      <c r="W75">
+        <v>0.2251619832706995</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3807374854634428</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2488759923499317</v>
+      </c>
+      <c r="C76">
+        <v>-63.04087328952566</v>
+      </c>
+      <c r="D76">
+        <v>60.95112671047434</v>
+      </c>
+      <c r="E76">
+        <v>113.392</v>
+      </c>
+      <c r="F76">
+        <v>133.792</v>
+      </c>
+      <c r="G76">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H76">
+        <v>160.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>27.4</v>
+      </c>
+      <c r="K76">
+        <v>15.4</v>
+      </c>
+      <c r="L76">
+        <v>12</v>
+      </c>
+      <c r="M76">
+        <v>31.9495296</v>
+      </c>
+      <c r="N76">
+        <v>-19.9495296</v>
+      </c>
+      <c r="O76">
+        <v>-2.992429440000001</v>
+      </c>
+      <c r="P76">
+        <v>-16.95710016</v>
+      </c>
+      <c r="Q76">
+        <v>-1.557100160000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3158451713935425</v>
+      </c>
+      <c r="T76">
+        <v>3.884869531087039</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.05633885764627972</v>
+      </c>
+      <c r="W76">
+        <v>0.2253462807940684</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3755923843085314</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2508759923499317</v>
+      </c>
+      <c r="C77">
+        <v>-65.42367787758961</v>
+      </c>
+      <c r="D77">
+        <v>60.37632212241041</v>
+      </c>
+      <c r="E77">
+        <v>115.2</v>
+      </c>
+      <c r="F77">
+        <v>135.6</v>
+      </c>
+      <c r="G77">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H77">
+        <v>160.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>27.4</v>
+      </c>
+      <c r="K77">
+        <v>15.4</v>
+      </c>
+      <c r="L77">
+        <v>12</v>
+      </c>
+      <c r="M77">
+        <v>32.38128</v>
+      </c>
+      <c r="N77">
+        <v>-20.38128</v>
+      </c>
+      <c r="O77">
+        <v>-3.057192000000001</v>
+      </c>
+      <c r="P77">
+        <v>-17.324088</v>
+      </c>
+      <c r="Q77">
+        <v>-1.924088000000005</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3269269782492841</v>
+      </c>
+      <c r="T77">
+        <v>4.040264312330521</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.05558767287766265</v>
+      </c>
+      <c r="W77">
+        <v>0.2255256637168142</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3705844858510843</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2528759923499317</v>
+      </c>
+      <c r="C78">
+        <v>-67.79574226855334</v>
+      </c>
+      <c r="D78">
+        <v>59.81225773144667</v>
+      </c>
+      <c r="E78">
+        <v>117.008</v>
+      </c>
+      <c r="F78">
+        <v>137.408</v>
+      </c>
+      <c r="G78">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H78">
+        <v>160.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>27.4</v>
+      </c>
+      <c r="K78">
+        <v>15.4</v>
+      </c>
+      <c r="L78">
+        <v>12</v>
+      </c>
+      <c r="M78">
+        <v>32.8130304</v>
+      </c>
+      <c r="N78">
+        <v>-20.8130304</v>
+      </c>
+      <c r="O78">
+        <v>-3.121954560000001</v>
+      </c>
+      <c r="P78">
+        <v>-17.69107584</v>
+      </c>
+      <c r="Q78">
+        <v>-2.291075840000005</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.338932269009671</v>
+      </c>
+      <c r="T78">
+        <v>4.208608658677627</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.05485625612927236</v>
+      </c>
+      <c r="W78">
+        <v>0.2257003260363298</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.365708374195149</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2548759923499316</v>
+      </c>
+      <c r="C79">
+        <v>-70.15736469630163</v>
+      </c>
+      <c r="D79">
+        <v>59.25863530369838</v>
+      </c>
+      <c r="E79">
+        <v>118.816</v>
+      </c>
+      <c r="F79">
+        <v>139.216</v>
+      </c>
+      <c r="G79">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H79">
+        <v>160.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>27.4</v>
+      </c>
+      <c r="K79">
+        <v>15.4</v>
+      </c>
+      <c r="L79">
+        <v>12</v>
+      </c>
+      <c r="M79">
+        <v>33.2447808</v>
+      </c>
+      <c r="N79">
+        <v>-21.2447808</v>
+      </c>
+      <c r="O79">
+        <v>-3.18671712</v>
+      </c>
+      <c r="P79">
+        <v>-18.05806368</v>
+      </c>
+      <c r="Q79">
+        <v>-2.658063680000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.351981498097048</v>
+      </c>
+      <c r="T79">
+        <v>4.391591643837524</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.05414383721850258</v>
+      </c>
+      <c r="W79">
+        <v>0.2258704516722216</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3609589147900172</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2568759923499317</v>
+      </c>
+      <c r="C80">
+        <v>-72.50883245417026</v>
+      </c>
+      <c r="D80">
+        <v>58.71516754582974</v>
+      </c>
+      <c r="E80">
+        <v>120.624</v>
+      </c>
+      <c r="F80">
+        <v>141.024</v>
+      </c>
+      <c r="G80">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H80">
+        <v>160.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>27.4</v>
+      </c>
+      <c r="K80">
+        <v>15.4</v>
+      </c>
+      <c r="L80">
+        <v>12</v>
+      </c>
+      <c r="M80">
+        <v>33.6765312</v>
+      </c>
+      <c r="N80">
+        <v>-21.6765312</v>
+      </c>
+      <c r="O80">
+        <v>-3.251479680000001</v>
+      </c>
+      <c r="P80">
+        <v>-18.42505152</v>
+      </c>
+      <c r="Q80">
+        <v>-3.025051520000002</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.366217020737823</v>
+      </c>
+      <c r="T80">
+        <v>4.591209445830139</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.05344968545929102</v>
+      </c>
+      <c r="W80">
+        <v>0.2260362151123213</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3563312363952734</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2588759923499316</v>
+      </c>
+      <c r="C81">
+        <v>-74.85042239207199</v>
+      </c>
+      <c r="D81">
+        <v>58.18157760792803</v>
+      </c>
+      <c r="E81">
+        <v>122.432</v>
+      </c>
+      <c r="F81">
+        <v>142.832</v>
+      </c>
+      <c r="G81">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H81">
+        <v>160.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>27.4</v>
+      </c>
+      <c r="K81">
+        <v>15.4</v>
+      </c>
+      <c r="L81">
+        <v>12</v>
+      </c>
+      <c r="M81">
+        <v>34.10828160000001</v>
+      </c>
+      <c r="N81">
+        <v>-22.10828160000001</v>
+      </c>
+      <c r="O81">
+        <v>-3.316242240000001</v>
+      </c>
+      <c r="P81">
+        <v>-18.79203936</v>
+      </c>
+      <c r="Q81">
+        <v>-3.392039360000005</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3818083074396241</v>
+      </c>
+      <c r="T81">
+        <v>4.809838467060146</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.05277310716233796</v>
+      </c>
+      <c r="W81">
+        <v>0.2261977820096337</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3518207144155864</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2608759923499317</v>
+      </c>
+      <c r="C82">
+        <v>-77.18240138675999</v>
+      </c>
+      <c r="D82">
+        <v>57.65759861324002</v>
+      </c>
+      <c r="E82">
+        <v>124.24</v>
+      </c>
+      <c r="F82">
+        <v>144.64</v>
+      </c>
+      <c r="G82">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H82">
+        <v>160.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>27.4</v>
+      </c>
+      <c r="K82">
+        <v>15.4</v>
+      </c>
+      <c r="L82">
+        <v>12</v>
+      </c>
+      <c r="M82">
+        <v>34.540032</v>
+      </c>
+      <c r="N82">
+        <v>-22.540032</v>
+      </c>
+      <c r="O82">
+        <v>-3.381004800000001</v>
+      </c>
+      <c r="P82">
+        <v>-19.1590272</v>
+      </c>
+      <c r="Q82">
+        <v>-3.759027200000006</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3989587228116053</v>
+      </c>
+      <c r="T82">
+        <v>5.050330390413152</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.05211344332280874</v>
+      </c>
+      <c r="W82">
+        <v>0.2263553097345133</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3474229554853915</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2628759923499317</v>
+      </c>
+      <c r="C83">
+        <v>-79.50502678690728</v>
+      </c>
+      <c r="D83">
+        <v>57.14297321309273</v>
+      </c>
+      <c r="E83">
+        <v>126.048</v>
+      </c>
+      <c r="F83">
+        <v>146.448</v>
+      </c>
+      <c r="G83">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H83">
+        <v>160.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>27.4</v>
+      </c>
+      <c r="K83">
+        <v>15.4</v>
+      </c>
+      <c r="L83">
+        <v>12</v>
+      </c>
+      <c r="M83">
+        <v>34.9717824</v>
+      </c>
+      <c r="N83">
+        <v>-22.9717824</v>
+      </c>
+      <c r="O83">
+        <v>-3.445767360000001</v>
+      </c>
+      <c r="P83">
+        <v>-19.52601504</v>
+      </c>
+      <c r="Q83">
+        <v>-4.126015040000002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4179144450648478</v>
+      </c>
+      <c r="T83">
+        <v>5.316137253066477</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.05147006747931727</v>
+      </c>
+      <c r="W83">
+        <v>0.2265089478859391</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3431337831954484</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2648759923499317</v>
+      </c>
+      <c r="C84">
+        <v>-81.81854683456139</v>
+      </c>
+      <c r="D84">
+        <v>56.63745316543864</v>
+      </c>
+      <c r="E84">
+        <v>127.856</v>
+      </c>
+      <c r="F84">
+        <v>148.256</v>
+      </c>
+      <c r="G84">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H84">
+        <v>160.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>27.4</v>
+      </c>
+      <c r="K84">
+        <v>15.4</v>
+      </c>
+      <c r="L84">
+        <v>12</v>
+      </c>
+      <c r="M84">
+        <v>35.40353280000001</v>
+      </c>
+      <c r="N84">
+        <v>-23.40353280000001</v>
+      </c>
+      <c r="O84">
+        <v>-3.510529920000002</v>
+      </c>
+      <c r="P84">
+        <v>-19.89300288</v>
+      </c>
+      <c r="Q84">
+        <v>-4.493002880000006</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4389763586795615</v>
+      </c>
+      <c r="T84">
+        <v>5.61147821157017</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.05084238372956949</v>
+      </c>
+      <c r="W84">
+        <v>0.2266588387653788</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3389492248637965</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2668759923499317</v>
+      </c>
+      <c r="C85">
+        <v>-84.12320106442475</v>
+      </c>
+      <c r="D85">
+        <v>56.14079893557528</v>
+      </c>
+      <c r="E85">
+        <v>129.664</v>
+      </c>
+      <c r="F85">
+        <v>150.064</v>
+      </c>
+      <c r="G85">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H85">
+        <v>160.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>27.4</v>
+      </c>
+      <c r="K85">
+        <v>15.4</v>
+      </c>
+      <c r="L85">
+        <v>12</v>
+      </c>
+      <c r="M85">
+        <v>35.83528320000001</v>
+      </c>
+      <c r="N85">
+        <v>-23.83528320000001</v>
+      </c>
+      <c r="O85">
+        <v>-3.575292480000002</v>
+      </c>
+      <c r="P85">
+        <v>-20.25999072</v>
+      </c>
+      <c r="Q85">
+        <v>-4.859990720000006</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4625161444842416</v>
+      </c>
+      <c r="T85">
+        <v>5.941565165191945</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.0502298248894542</v>
+      </c>
+      <c r="W85">
+        <v>0.2268051178163984</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.334865499263028</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2688759923499316</v>
+      </c>
+      <c r="C86">
+        <v>-86.41922068230984</v>
+      </c>
+      <c r="D86">
+        <v>55.65277931769018</v>
+      </c>
+      <c r="E86">
+        <v>131.472</v>
+      </c>
+      <c r="F86">
+        <v>151.872</v>
+      </c>
+      <c r="G86">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H86">
+        <v>160.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>27.4</v>
+      </c>
+      <c r="K86">
+        <v>15.4</v>
+      </c>
+      <c r="L86">
+        <v>12</v>
+      </c>
+      <c r="M86">
+        <v>36.2670336</v>
+      </c>
+      <c r="N86">
+        <v>-24.2670336</v>
+      </c>
+      <c r="O86">
+        <v>-3.640055040000001</v>
+      </c>
+      <c r="P86">
+        <v>-20.62697856</v>
+      </c>
+      <c r="Q86">
+        <v>-5.226978560000006</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4889984035145064</v>
+      </c>
+      <c r="T86">
+        <v>6.312912988016438</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.04963185078362737</v>
+      </c>
+      <c r="W86">
+        <v>0.2269479140328698</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3308790052241823</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2708759923499316</v>
+      </c>
+      <c r="C87">
+        <v>-88.70682892402553</v>
+      </c>
+      <c r="D87">
+        <v>55.17317107597447</v>
+      </c>
+      <c r="E87">
+        <v>133.28</v>
+      </c>
+      <c r="F87">
+        <v>153.68</v>
+      </c>
+      <c r="G87">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H87">
+        <v>160.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>27.4</v>
+      </c>
+      <c r="K87">
+        <v>15.4</v>
+      </c>
+      <c r="L87">
+        <v>12</v>
+      </c>
+      <c r="M87">
+        <v>36.698784</v>
+      </c>
+      <c r="N87">
+        <v>-24.698784</v>
+      </c>
+      <c r="O87">
+        <v>-3.704817600000001</v>
+      </c>
+      <c r="P87">
+        <v>-20.9939664</v>
+      </c>
+      <c r="Q87">
+        <v>-5.593966400000003</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5190116304154736</v>
+      </c>
+      <c r="T87">
+        <v>6.733773853884202</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.04904794665676116</v>
+      </c>
+      <c r="W87">
+        <v>0.2270873503383654</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3269863110450744</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2728759923499317</v>
+      </c>
+      <c r="C88">
+        <v>-90.98624139586495</v>
+      </c>
+      <c r="D88">
+        <v>54.70175860413504</v>
+      </c>
+      <c r="E88">
+        <v>135.088</v>
+      </c>
+      <c r="F88">
+        <v>155.488</v>
+      </c>
+      <c r="G88">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H88">
+        <v>160.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>27.4</v>
+      </c>
+      <c r="K88">
+        <v>15.4</v>
+      </c>
+      <c r="L88">
+        <v>12</v>
+      </c>
+      <c r="M88">
+        <v>37.1305344</v>
+      </c>
+      <c r="N88">
+        <v>-25.1305344</v>
+      </c>
+      <c r="O88">
+        <v>-3.769580160000001</v>
+      </c>
+      <c r="P88">
+        <v>-21.36095424</v>
+      </c>
+      <c r="Q88">
+        <v>-5.960954240000003</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.553312461159436</v>
+      </c>
+      <c r="T88">
+        <v>7.214757700590216</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.04847762169563603</v>
+      </c>
+      <c r="W88">
+        <v>0.2272235439390821</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3231841446375735</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2748759923499317</v>
+      </c>
+      <c r="C89">
+        <v>-93.257666397786</v>
+      </c>
+      <c r="D89">
+        <v>54.23833360221403</v>
+      </c>
+      <c r="E89">
+        <v>136.896</v>
+      </c>
+      <c r="F89">
+        <v>157.296</v>
+      </c>
+      <c r="G89">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H89">
+        <v>160.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>27.4</v>
+      </c>
+      <c r="K89">
+        <v>15.4</v>
+      </c>
+      <c r="L89">
+        <v>12</v>
+      </c>
+      <c r="M89">
+        <v>37.56228480000001</v>
+      </c>
+      <c r="N89">
+        <v>-25.56228480000001</v>
+      </c>
+      <c r="O89">
+        <v>-3.834342720000002</v>
+      </c>
+      <c r="P89">
+        <v>-21.72794208000001</v>
+      </c>
+      <c r="Q89">
+        <v>-6.327942080000007</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5928903427870849</v>
+      </c>
+      <c r="T89">
+        <v>7.76973906217408</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.04792040765315746</v>
+      </c>
+      <c r="W89">
+        <v>0.227356606652426</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.319469384354383</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2768759923499317</v>
+      </c>
+      <c r="C90">
+        <v>-95.52130523030206</v>
+      </c>
+      <c r="D90">
+        <v>53.78269476969795</v>
+      </c>
+      <c r="E90">
+        <v>138.704</v>
+      </c>
+      <c r="F90">
+        <v>159.104</v>
+      </c>
+      <c r="G90">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H90">
+        <v>160.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>27.4</v>
+      </c>
+      <c r="K90">
+        <v>15.4</v>
+      </c>
+      <c r="L90">
+        <v>12</v>
+      </c>
+      <c r="M90">
+        <v>37.99403520000001</v>
+      </c>
+      <c r="N90">
+        <v>-25.99403520000001</v>
+      </c>
+      <c r="O90">
+        <v>-3.899105280000001</v>
+      </c>
+      <c r="P90">
+        <v>-22.09492992000001</v>
+      </c>
+      <c r="Q90">
+        <v>-6.694929920000007</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.639064538019342</v>
+      </c>
+      <c r="T90">
+        <v>8.417217317355254</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.04737585756618976</v>
+      </c>
+      <c r="W90">
+        <v>0.2274866452131939</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.315839050441265</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2788759923499317</v>
+      </c>
+      <c r="C91">
+        <v>-97.77735248603352</v>
+      </c>
+      <c r="D91">
+        <v>53.33464751396649</v>
+      </c>
+      <c r="E91">
+        <v>140.512</v>
+      </c>
+      <c r="F91">
+        <v>160.912</v>
+      </c>
+      <c r="G91">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H91">
+        <v>160.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>27.4</v>
+      </c>
+      <c r="K91">
+        <v>15.4</v>
+      </c>
+      <c r="L91">
+        <v>12</v>
+      </c>
+      <c r="M91">
+        <v>38.4257856</v>
+      </c>
+      <c r="N91">
+        <v>-26.4257856</v>
+      </c>
+      <c r="O91">
+        <v>-3.963867840000001</v>
+      </c>
+      <c r="P91">
+        <v>-22.46191776</v>
+      </c>
+      <c r="Q91">
+        <v>-7.061917760000004</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6936340414756459</v>
+      </c>
+      <c r="T91">
+        <v>9.182418891660276</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.04684354455982808</v>
+      </c>
+      <c r="W91">
+        <v>0.2276137615591131</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3122902970655205</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2808759923499317</v>
+      </c>
+      <c r="C92">
+        <v>-100.0259963268062</v>
+      </c>
+      <c r="D92">
+        <v>52.89400367319381</v>
+      </c>
+      <c r="E92">
+        <v>142.32</v>
+      </c>
+      <c r="F92">
+        <v>162.72</v>
+      </c>
+      <c r="G92">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H92">
+        <v>160.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>27.4</v>
+      </c>
+      <c r="K92">
+        <v>15.4</v>
+      </c>
+      <c r="L92">
+        <v>12</v>
+      </c>
+      <c r="M92">
+        <v>38.85753600000001</v>
+      </c>
+      <c r="N92">
+        <v>-26.85753600000001</v>
+      </c>
+      <c r="O92">
+        <v>-4.028630400000002</v>
+      </c>
+      <c r="P92">
+        <v>-22.82890560000001</v>
+      </c>
+      <c r="Q92">
+        <v>-7.428905600000011</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7591174456232106</v>
+      </c>
+      <c r="T92">
+        <v>10.1006607808263</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.04632306073138553</v>
+      </c>
+      <c r="W92">
+        <v>0.2277380530973451</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3088204048759036</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2828759923499317</v>
+      </c>
+      <c r="C93">
+        <v>-102.2674187471265</v>
+      </c>
+      <c r="D93">
+        <v>52.4605812528735</v>
+      </c>
+      <c r="E93">
+        <v>144.128</v>
+      </c>
+      <c r="F93">
+        <v>164.528</v>
+      </c>
+      <c r="G93">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H93">
+        <v>160.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>27.4</v>
+      </c>
+      <c r="K93">
+        <v>15.4</v>
+      </c>
+      <c r="L93">
+        <v>12</v>
+      </c>
+      <c r="M93">
+        <v>39.28928640000001</v>
+      </c>
+      <c r="N93">
+        <v>-27.28928640000001</v>
+      </c>
+      <c r="O93">
+        <v>-4.093392960000002</v>
+      </c>
+      <c r="P93">
+        <v>-23.19589344000001</v>
+      </c>
+      <c r="Q93">
+        <v>-7.795893440000008</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8391527173591229</v>
+      </c>
+      <c r="T93">
+        <v>11.22295642314034</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.04581401610796372</v>
+      </c>
+      <c r="W93">
+        <v>0.2278596129534183</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3054267740530914</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2848759923499317</v>
+      </c>
+      <c r="C94">
+        <v>-104.5017958248081</v>
+      </c>
+      <c r="D94">
+        <v>52.03420417519196</v>
+      </c>
+      <c r="E94">
+        <v>145.936</v>
+      </c>
+      <c r="F94">
+        <v>166.336</v>
+      </c>
+      <c r="G94">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H94">
+        <v>160.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>27.4</v>
+      </c>
+      <c r="K94">
+        <v>15.4</v>
+      </c>
+      <c r="L94">
+        <v>12</v>
+      </c>
+      <c r="M94">
+        <v>39.72103680000001</v>
+      </c>
+      <c r="N94">
+        <v>-27.72103680000001</v>
+      </c>
+      <c r="O94">
+        <v>-4.158155520000002</v>
+      </c>
+      <c r="P94">
+        <v>-23.56288128000001</v>
+      </c>
+      <c r="Q94">
+        <v>-8.162881280000008</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9391968070290135</v>
+      </c>
+      <c r="T94">
+        <v>12.62582597603289</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.04531603767200759</v>
+      </c>
+      <c r="W94">
+        <v>0.2279785302039246</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3021069178133839</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2868759923499317</v>
+      </c>
+      <c r="C95">
+        <v>-106.7292979594748</v>
+      </c>
+      <c r="D95">
+        <v>51.61470204052516</v>
+      </c>
+      <c r="E95">
+        <v>147.744</v>
+      </c>
+      <c r="F95">
+        <v>168.144</v>
+      </c>
+      <c r="G95">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H95">
+        <v>160.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>27.4</v>
+      </c>
+      <c r="K95">
+        <v>15.4</v>
+      </c>
+      <c r="L95">
+        <v>12</v>
+      </c>
+      <c r="M95">
+        <v>40.15278720000001</v>
+      </c>
+      <c r="N95">
+        <v>-28.15278720000001</v>
+      </c>
+      <c r="O95">
+        <v>-4.222918080000001</v>
+      </c>
+      <c r="P95">
+        <v>-23.92986912000001</v>
+      </c>
+      <c r="Q95">
+        <v>-8.529869120000008</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.067824922318873</v>
+      </c>
+      <c r="T95">
+        <v>14.42951540118044</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.04482876844972795</v>
+      </c>
+      <c r="W95">
+        <v>0.228094890094205</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2988584563315195</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2888759923499317</v>
+      </c>
+      <c r="C96">
+        <v>-108.95009009962</v>
+      </c>
+      <c r="D96">
+        <v>51.20190990038</v>
+      </c>
+      <c r="E96">
+        <v>149.552</v>
+      </c>
+      <c r="F96">
+        <v>169.952</v>
+      </c>
+      <c r="G96">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H96">
+        <v>160.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>27.4</v>
+      </c>
+      <c r="K96">
+        <v>15.4</v>
+      </c>
+      <c r="L96">
+        <v>12</v>
+      </c>
+      <c r="M96">
+        <v>40.58453760000001</v>
+      </c>
+      <c r="N96">
+        <v>-28.58453760000001</v>
+      </c>
+      <c r="O96">
+        <v>-4.287680640000002</v>
+      </c>
+      <c r="P96">
+        <v>-24.29685696000001</v>
+      </c>
+      <c r="Q96">
+        <v>-8.896856960000012</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.239329076038685</v>
+      </c>
+      <c r="T96">
+        <v>16.83443463471052</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.04435186665770956</v>
+      </c>
+      <c r="W96">
+        <v>0.228208774242139</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.295679111051397</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2908759923499317</v>
+      </c>
+      <c r="C97">
+        <v>-111.1643319588551</v>
+      </c>
+      <c r="D97">
+        <v>50.79566804114493</v>
+      </c>
+      <c r="E97">
+        <v>151.36</v>
+      </c>
+      <c r="F97">
+        <v>171.76</v>
+      </c>
+      <c r="G97">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H97">
+        <v>160.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>27.4</v>
+      </c>
+      <c r="K97">
+        <v>15.4</v>
+      </c>
+      <c r="L97">
+        <v>12</v>
+      </c>
+      <c r="M97">
+        <v>41.01628800000001</v>
+      </c>
+      <c r="N97">
+        <v>-29.01628800000001</v>
+      </c>
+      <c r="O97">
+        <v>-4.352443200000002</v>
+      </c>
+      <c r="P97">
+        <v>-24.66384480000001</v>
+      </c>
+      <c r="Q97">
+        <v>-9.263844800000008</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.479434891246423</v>
+      </c>
+      <c r="T97">
+        <v>20.20132156165264</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04388500490341787</v>
+      </c>
+      <c r="W97">
+        <v>0.2283202608290638</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2925666993561191</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2928759923499317</v>
+      </c>
+      <c r="C98">
+        <v>-113.3721782219462</v>
+      </c>
+      <c r="D98">
+        <v>50.39582177805382</v>
+      </c>
+      <c r="E98">
+        <v>153.168</v>
+      </c>
+      <c r="F98">
+        <v>173.568</v>
+      </c>
+      <c r="G98">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H98">
+        <v>160.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>27.4</v>
+      </c>
+      <c r="K98">
+        <v>15.4</v>
+      </c>
+      <c r="L98">
+        <v>12</v>
+      </c>
+      <c r="M98">
+        <v>41.4480384</v>
+      </c>
+      <c r="N98">
+        <v>-29.4480384</v>
+      </c>
+      <c r="O98">
+        <v>-4.417205760000001</v>
+      </c>
+      <c r="P98">
+        <v>-25.03083264</v>
+      </c>
+      <c r="Q98">
+        <v>-9.630832640000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.839593614058024</v>
+      </c>
+      <c r="T98">
+        <v>25.25165195206574</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04342786943567395</v>
+      </c>
+      <c r="W98">
+        <v>0.228429424778761</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2895191295711597</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2948759923499317</v>
+      </c>
+      <c r="C99">
+        <v>-115.5737787411951</v>
+      </c>
+      <c r="D99">
+        <v>50.00222125880493</v>
+      </c>
+      <c r="E99">
+        <v>154.976</v>
+      </c>
+      <c r="F99">
+        <v>175.376</v>
+      </c>
+      <c r="G99">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H99">
+        <v>160.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>27.4</v>
+      </c>
+      <c r="K99">
+        <v>15.4</v>
+      </c>
+      <c r="L99">
+        <v>12</v>
+      </c>
+      <c r="M99">
+        <v>41.8797888</v>
+      </c>
+      <c r="N99">
+        <v>-29.8797888</v>
+      </c>
+      <c r="O99">
+        <v>-4.481968320000001</v>
+      </c>
+      <c r="P99">
+        <v>-25.39782048</v>
+      </c>
+      <c r="Q99">
+        <v>-9.997820480000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.439858152077367</v>
+      </c>
+      <c r="T99">
+        <v>33.66886926942099</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04298015944149174</v>
+      </c>
+      <c r="W99">
+        <v>0.2285363379253718</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2865343962766116</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2968759923499317</v>
+      </c>
+      <c r="C100">
+        <v>-117.7692787236886</v>
+      </c>
+      <c r="D100">
+        <v>49.61472127631136</v>
+      </c>
+      <c r="E100">
+        <v>156.784</v>
+      </c>
+      <c r="F100">
+        <v>177.184</v>
+      </c>
+      <c r="G100">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H100">
+        <v>160.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>27.4</v>
+      </c>
+      <c r="K100">
+        <v>15.4</v>
+      </c>
+      <c r="L100">
+        <v>12</v>
+      </c>
+      <c r="M100">
+        <v>42.3115392</v>
+      </c>
+      <c r="N100">
+        <v>-30.3115392</v>
+      </c>
+      <c r="O100">
+        <v>-4.54673088</v>
+      </c>
+      <c r="P100">
+        <v>-25.76480832</v>
+      </c>
+      <c r="Q100">
+        <v>-10.36480832</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.64038722811605</v>
+      </c>
+      <c r="T100">
+        <v>50.50330390413148</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.04254158638596633</v>
+      </c>
+      <c r="W100">
+        <v>0.2286410691710313</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2836105759064421</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2988759923499317</v>
+      </c>
+      <c r="C101">
+        <v>-119.958818909909</v>
+      </c>
+      <c r="D101">
+        <v>49.23318109009105</v>
+      </c>
+      <c r="E101">
+        <v>158.592</v>
+      </c>
+      <c r="F101">
+        <v>178.992</v>
+      </c>
+      <c r="G101">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H101">
+        <v>160.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>27.4</v>
+      </c>
+      <c r="K101">
+        <v>15.4</v>
+      </c>
+      <c r="L101">
+        <v>12</v>
+      </c>
+      <c r="M101">
+        <v>42.7432896</v>
+      </c>
+      <c r="N101">
+        <v>-30.7432896</v>
+      </c>
+      <c r="O101">
+        <v>-4.611493440000001</v>
+      </c>
+      <c r="P101">
+        <v>-26.13179616</v>
+      </c>
+      <c r="Q101">
+        <v>-10.73179616000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.241974456232098</v>
+      </c>
+      <c r="T101">
+        <v>101.0066078082629</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.04211187339216867</v>
+      </c>
+      <c r="W101">
+        <v>0.2287436846339501</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2807458226144578</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
